--- a/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
+++ b/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -1628,28 +1628,28 @@
         <v>186</v>
       </c>
     </row>
-    <row r="43" ht="21" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>30.750.1502</t>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -1659,21 +1659,21 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -1681,14 +1681,14 @@
       <c r="B45" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -1700,28 +1700,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
+    <row r="46" ht="21" customHeight="1">
       <c r="A46" s="14" t="n"/>
       <c r="B46" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
@@ -1729,23 +1729,23 @@
       <c r="B47" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>30.120.2016</t>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>35.750.2001 (montaj)</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -1755,414 +1755,406 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="49" ht="31.5" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="9" t="n">
         <v>18</v>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.740.1106 (montaj)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="50" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="14" t="n"/>
       <c r="B50" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="51" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
       <c r="A51" s="14" t="n"/>
       <c r="B51" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>35.740.5406 (montaj)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="A52" s="15" t="n"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="14" t="n"/>
       <c r="B52" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>30.190.1304</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="14" t="n"/>
+      <c r="B53" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="54" ht="31.5" customHeight="1">
+      <c r="A54" s="14" t="n"/>
+      <c r="B54" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="14" t="n"/>
+      <c r="B55" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>361.2</v>
+      </c>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="14" t="n"/>
+      <c r="B56" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>361.2</v>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1304</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
           <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F57" s="13" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>&lt; Kümes B Blok &gt;   —   inşaat alanı 1.106.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>A blok ile geometrik olarak birebir aynıdır.</t>
         </is>
       </c>
-      <c r="B55" s="39" t="n"/>
-      <c r="C55" s="39" t="n"/>
-      <c r="D55" s="39" t="n"/>
-      <c r="E55" s="39" t="n"/>
-      <c r="F55" s="40" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="B60" s="39" t="n"/>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="39" t="n"/>
+      <c r="F60" s="40" t="n"/>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="B62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>15.120.1001</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D62" s="11" t="inlineStr">
         <is>
           <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F62" s="13" t="n">
         <v>1684.385</v>
       </c>
     </row>
-    <row r="58" ht="31.5" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="63" ht="31.5" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="B63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D63" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F63" s="13" t="n">
         <v>31.429</v>
       </c>
     </row>
-    <row r="59" ht="31.5" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="64" ht="31.5" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="B64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F64" s="13" t="n">
         <v>278.34</v>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="B65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D65" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F65" s="13" t="n">
         <v>551.26</v>
-      </c>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="14" t="n"/>
-      <c r="B62" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>7.288</v>
-      </c>
-    </row>
-    <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="15" t="n"/>
-      <c r="B63" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1002</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="n">
-        <v>3.637</v>
-      </c>
-    </row>
-    <row r="64" ht="21" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>Çelik yapım-imalat işleri</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>15.165.1003</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="n">
-        <v>44.048</v>
-      </c>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="15" t="n"/>
-      <c r="B65" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>15.550.1202</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="n">
-        <v>674</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B66" s="9" t="n">
@@ -2170,75 +2162,75 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>507.91</v>
-      </c>
-    </row>
-    <row r="67" ht="14" customHeight="1">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
       <c r="A67" s="14" t="n"/>
       <c r="B67" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>49.85</v>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
+        <v>7.288</v>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
       <c r="A68" s="15" t="n"/>
       <c r="B68" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>45</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B69" s="9" t="n">
@@ -2246,203 +2238,203 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1204.98</v>
+        <v>44.048</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="14" t="n"/>
+      <c r="A70" s="15" t="n"/>
       <c r="B70" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
+          <t>15.550.1202</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Tuğla ve duvar işleri</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>15.225.1010</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>507.91</v>
+      </c>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="14" t="n"/>
+      <c r="B72" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>15.225.1410</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>49.85</v>
+      </c>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="15" t="n"/>
+      <c r="B73" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>15.225.1004</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>Çatı ve sundurma işleri</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>1204.98</v>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="14" t="n"/>
+      <c r="B75" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
           <t>TKDK-0115</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D75" s="11" t="inlineStr">
         <is>
           <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F70" s="13" t="n">
+      <c r="F75" s="13" t="n">
         <v>319.2</v>
-      </c>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="15" t="n"/>
-      <c r="B71" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>15.315.1001</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="n">
-        <v>51.2</v>
-      </c>
-    </row>
-    <row r="72" ht="21" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="n">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="73" ht="21" customHeight="1">
-      <c r="A73" s="14" t="n"/>
-      <c r="B73" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F73" s="13" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="74" ht="21" customHeight="1">
-      <c r="A74" s="15" t="n"/>
-      <c r="B74" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>15.550.1002</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="n">
-        <v>54.315</v>
-      </c>
-    </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>15.275.1116</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F75" s="13" t="n">
-        <v>557.76</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="15" t="n"/>
       <c r="B76" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>647.76</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B77" s="9" t="n">
@@ -2450,12 +2442,12 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -2464,298 +2456,306 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>557.76</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="15" t="n"/>
+      <c r="A78" s="14" t="n"/>
       <c r="B78" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="15" t="n"/>
+      <c r="B79" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1002</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>54.315</v>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>15.275.1116</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>557.76</v>
+      </c>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="15" t="n"/>
+      <c r="B81" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>15.275.1117</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>647.76</v>
+      </c>
+    </row>
+    <row r="82" ht="21" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>15.540.1606</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>557.76</v>
+      </c>
+    </row>
+    <row r="83" ht="21" customHeight="1">
+      <c r="A83" s="15" t="n"/>
+      <c r="B83" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
           <t>15.540.1537</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
         <is>
           <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="E83" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F78" s="13" t="n">
+      <c r="F83" s="13" t="n">
         <v>612.76</v>
       </c>
     </row>
-    <row r="79" ht="31.5" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="84" ht="31.5" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
-      <c r="B79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="B84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>TKDK-0177</t>
         </is>
       </c>
-      <c r="D79" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr">
         <is>
           <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F79" s="13" t="n">
+      <c r="F84" s="13" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="80" ht="21" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>Kanalizasyon işleri</t>
         </is>
       </c>
-      <c r="B80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="B85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
         <is>
           <t>43.527.1001</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F80" s="13" t="n">
+      <c r="F85" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="81" ht="21" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="86" ht="21" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>30.100.2105</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="B86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>35.100.2105</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
         <is>
           <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F81" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" ht="21" customHeight="1">
-      <c r="A82" s="14" t="n"/>
-      <c r="B82" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>30.110.1102</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="14" t="n"/>
-      <c r="B83" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F83" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" ht="21" customHeight="1">
-      <c r="A84" s="14" t="n"/>
-      <c r="B84" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>30.140.3104</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="85" ht="21" customHeight="1">
-      <c r="A85" s="14" t="n"/>
-      <c r="B85" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>30.170.1602</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" ht="21" customHeight="1">
-      <c r="A86" s="14" t="n"/>
-      <c r="B86" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>30.170.1601</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
       <c r="F86" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" ht="14" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" ht="21" customHeight="1">
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="14" t="n"/>
       <c r="B89" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -2764,94 +2764,94 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="14" t="n"/>
       <c r="B90" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="14" t="n"/>
       <c r="B91" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="92" ht="21" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
       <c r="A92" s="14" t="n"/>
       <c r="B92" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" ht="21" customHeight="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
       <c r="A93" s="14" t="n"/>
       <c r="B93" s="9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
@@ -2860,427 +2860,452 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>16</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="14" t="n"/>
       <c r="B94" s="9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" ht="14" customHeight="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
       <c r="A95" s="14" t="n"/>
       <c r="B95" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" ht="14" customHeight="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
       <c r="A96" s="14" t="n"/>
       <c r="B96" s="9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" ht="21" customHeight="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="97" ht="14" customHeight="1">
       <c r="A97" s="14" t="n"/>
       <c r="B97" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
+        <v>12</v>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="98" ht="31.5" customHeight="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1">
       <c r="A98" s="14" t="n"/>
       <c r="B98" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+        <v>13</v>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>502</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="14" t="n"/>
       <c r="B99" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
+        <v>14</v>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="14" t="n"/>
       <c r="B100" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>35.750.2001</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="14" t="n"/>
+      <c r="B101" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>35.750.2001 (montaj)</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" ht="21" customHeight="1">
+      <c r="A102" s="14" t="n"/>
+      <c r="B102" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>35.740.1106</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" ht="21" customHeight="1">
+      <c r="A103" s="14" t="n"/>
+      <c r="B103" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>35.740.1106 (montaj)</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="14" t="n"/>
+      <c r="B104" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>35.740.5406</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="14" t="n"/>
+      <c r="B105" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>35.740.5406 (montaj)</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="14" t="n"/>
+      <c r="B106" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>35.120.2016</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" ht="21" customHeight="1">
+      <c r="A107" s="14" t="n"/>
+      <c r="B107" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="108" ht="31.5" customHeight="1">
+      <c r="A108" s="14" t="n"/>
+      <c r="B108" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="109" ht="21" customHeight="1">
+      <c r="A109" s="14" t="n"/>
+      <c r="B109" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>361.2</v>
+      </c>
+    </row>
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="14" t="n"/>
+      <c r="B110" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>35.190.1101 (montaj)</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D110" s="11" t="inlineStr">
         <is>
           <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
-      <c r="E100" s="12" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F100" s="13" t="n">
+      <c r="F110" s="13" t="n">
         <v>361.2</v>
-      </c>
-    </row>
-    <row r="101" ht="21" customHeight="1">
-      <c r="A101" s="15" t="n"/>
-      <c r="B101" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t>30.190.1304</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Gübre Çukuru &gt;   —   inşaat alanı 115.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
-        </is>
-      </c>
-      <c r="B104" s="39" t="n"/>
-      <c r="C104" s="39" t="n"/>
-      <c r="D104" s="39" t="n"/>
-      <c r="E104" s="39" t="n"/>
-      <c r="F104" s="40" t="n"/>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D106" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F106" s="13" t="n">
-        <v>542.7</v>
-      </c>
-    </row>
-    <row r="107" ht="31.5" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F107" s="13" t="n">
-        <v>11.934</v>
-      </c>
-    </row>
-    <row r="108" ht="31.5" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F108" s="13" t="n">
-        <v>93.19</v>
-      </c>
-    </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F109" s="13" t="n">
-        <v>363.26</v>
-      </c>
-    </row>
-    <row r="110" ht="21" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F110" s="13" t="n">
-        <v>7.599</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="15" t="n"/>
       <c r="B111" s="9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5639999999999999</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
+          <t>&lt; Gübre Çukuru &gt;   —   inşaat alanı 115.00 m²</t>
         </is>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
+          <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
         </is>
       </c>
       <c r="B114" s="39" t="n"/>
@@ -3346,7 +3371,7 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>142</v>
+        <v>542.7</v>
       </c>
     </row>
     <row r="117" ht="31.5" customHeight="1">
@@ -3374,7 +3399,7 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>1.984</v>
+        <v>11.934</v>
       </c>
     </row>
     <row r="118" ht="31.5" customHeight="1">
@@ -3402,7 +3427,7 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>20.85</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
@@ -3430,7 +3455,7 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>127.2</v>
+        <v>363.26</v>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -3458,940 +3483,936 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>1.657</v>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
-        </is>
-      </c>
-      <c r="B123" s="39" t="n"/>
-      <c r="C123" s="39" t="n"/>
-      <c r="D123" s="39" t="n"/>
-      <c r="E123" s="39" t="n"/>
-      <c r="F123" s="40" t="n"/>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+        <v>7.599</v>
+      </c>
+    </row>
+    <row r="121" ht="21" customHeight="1">
+      <c r="A121" s="15" t="n"/>
+      <c r="B121" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
+        </is>
+      </c>
+      <c r="B124" s="39" t="n"/>
+      <c r="C124" s="39" t="n"/>
+      <c r="D124" s="39" t="n"/>
+      <c r="E124" s="39" t="n"/>
+      <c r="F124" s="40" t="n"/>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="B126" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D126" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="E126" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F125" s="13" t="n">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="126" ht="31.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D126" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E126" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F126" s="13" t="n">
-        <v>0.484</v>
+        <v>142</v>
       </c>
     </row>
     <row r="127" ht="31.5" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>1.984</v>
+      </c>
+    </row>
+    <row r="128" ht="31.5" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="B128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D128" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E127" s="12" t="inlineStr">
+      <c r="E128" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F127" s="13" t="n">
-        <v>6.175</v>
-      </c>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="F128" s="13" t="n">
+        <v>20.85</v>
+      </c>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="B129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E128" s="12" t="inlineStr">
+      <c r="E129" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F128" s="13" t="n">
-        <v>41.4</v>
-      </c>
-    </row>
-    <row r="129" ht="21" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="F129" s="13" t="n">
+        <v>127.2</v>
+      </c>
+    </row>
+    <row r="130" ht="21" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="B130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E129" s="12" t="inlineStr">
+      <c r="E130" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F129" s="13" t="n">
-        <v>0.587</v>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
-        </is>
-      </c>
-      <c r="B132" s="39" t="n"/>
-      <c r="C132" s="39" t="n"/>
-      <c r="D132" s="39" t="n"/>
-      <c r="E132" s="39" t="n"/>
-      <c r="F132" s="40" t="n"/>
-    </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
+      <c r="F130" s="13" t="n">
+        <v>1.657</v>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
+        </is>
+      </c>
+      <c r="B133" s="39" t="n"/>
+      <c r="C133" s="39" t="n"/>
+      <c r="D133" s="39" t="n"/>
+      <c r="E133" s="39" t="n"/>
+      <c r="F133" s="40" t="n"/>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="D134" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="E134" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F133" s="7" t="inlineStr">
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="14" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="B135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D135" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E135" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F134" s="13" t="n">
-        <v>48.02</v>
-      </c>
-    </row>
-    <row r="135" ht="31.5" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F135" s="13" t="n">
-        <v>1.922</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="136" ht="31.5" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>0.484</v>
+      </c>
+    </row>
+    <row r="137" ht="31.5" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="B137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E136" s="12" t="inlineStr">
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F136" s="13" t="n">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="F137" s="13" t="n">
+        <v>6.175</v>
+      </c>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E137" s="12" t="inlineStr">
+      <c r="E138" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F137" s="13" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="138" ht="21" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="F138" s="13" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="139" ht="21" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="B139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E138" s="12" t="inlineStr">
+      <c r="E139" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F138" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="24" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
-        </is>
-      </c>
-      <c r="B141" s="39" t="n"/>
-      <c r="C141" s="39" t="n"/>
-      <c r="D141" s="39" t="n"/>
-      <c r="E141" s="39" t="n"/>
-      <c r="F141" s="40" t="n"/>
-    </row>
-    <row r="142" ht="28" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
+      <c r="F139" s="13" t="n">
+        <v>0.587</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="24" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+        </is>
+      </c>
+      <c r="B142" s="39" t="n"/>
+      <c r="C142" s="39" t="n"/>
+      <c r="D142" s="39" t="n"/>
+      <c r="E142" s="39" t="n"/>
+      <c r="F142" s="40" t="n"/>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="B144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D144" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E144" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F143" s="13" t="n">
-        <v>106.5</v>
-      </c>
-    </row>
-    <row r="144" ht="31.5" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D144" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F144" s="13" t="n">
-        <v>1.344</v>
+        <v>48.02</v>
       </c>
     </row>
     <row r="145" ht="31.5" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="n">
+        <v>1.922</v>
+      </c>
+    </row>
+    <row r="146" ht="31.5" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
+      <c r="B146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D145" s="11" t="inlineStr">
+      <c r="D146" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="E146" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F145" s="13" t="n">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="F146" s="13" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F146" s="13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="147" ht="21" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="F147" s="13" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="148" ht="21" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D147" s="11" t="inlineStr">
+      <c r="D148" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E147" s="12" t="inlineStr">
+      <c r="E148" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F147" s="13" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
-        </is>
-      </c>
-      <c r="B150" s="39" t="n"/>
-      <c r="C150" s="39" t="n"/>
-      <c r="D150" s="39" t="n"/>
-      <c r="E150" s="39" t="n"/>
-      <c r="F150" s="40" t="n"/>
-    </row>
-    <row r="151" ht="28" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
+      <c r="F148" s="13" t="n">
+        <v>0.757</v>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="24" customHeight="1">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
+        </is>
+      </c>
+      <c r="B151" s="39" t="n"/>
+      <c r="C151" s="39" t="n"/>
+      <c r="D151" s="39" t="n"/>
+      <c r="E151" s="39" t="n"/>
+      <c r="F151" s="40" t="n"/>
+    </row>
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B151" s="7" t="inlineStr">
+      <c r="B152" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C151" s="7" t="inlineStr">
+      <c r="C152" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D151" s="7" t="inlineStr">
+      <c r="D152" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E151" s="7" t="inlineStr">
+      <c r="E152" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F151" s="7" t="inlineStr">
+      <c r="F152" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="B153" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D152" s="11" t="inlineStr">
+      <c r="D153" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E152" s="12" t="inlineStr">
+      <c r="E153" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F152" s="13" t="n">
-        <v>88.75</v>
-      </c>
-    </row>
-    <row r="153" ht="31.5" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F153" s="13" t="n">
-        <v>1.024</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="154" ht="31.5" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B154" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="155" ht="31.5" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B154" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
+      <c r="B155" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D154" s="11" t="inlineStr">
+      <c r="D155" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E154" s="12" t="inlineStr">
+      <c r="E155" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F154" s="13" t="n">
+      <c r="F155" s="13" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F156" s="13" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="157" ht="21" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B157" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="n">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="24" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
+        </is>
+      </c>
+      <c r="B160" s="39" t="n"/>
+      <c r="C160" s="39" t="n"/>
+      <c r="D160" s="39" t="n"/>
+      <c r="E160" s="39" t="n"/>
+      <c r="F160" s="40" t="n"/>
+    </row>
+    <row r="161" ht="28" customHeight="1">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B162" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D162" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F162" s="13" t="n">
+        <v>88.75</v>
+      </c>
+    </row>
+    <row r="163" ht="31.5" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B163" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E163" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F163" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="164" ht="31.5" customHeight="1">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B164" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F164" s="13" t="n">
         <v>12.3</v>
-      </c>
-    </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F155" s="13" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="156" ht="21" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D156" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F156" s="13" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
-        </is>
-      </c>
-      <c r="B159" s="39" t="n"/>
-      <c r="C159" s="39" t="n"/>
-      <c r="D159" s="39" t="n"/>
-      <c r="E159" s="39" t="n"/>
-      <c r="F159" s="40" t="n"/>
-    </row>
-    <row r="160" ht="28" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D160" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B161" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C161" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1001</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F161" s="13" t="n">
-        <v>260.943</v>
-      </c>
-    </row>
-    <row r="162" ht="31.5" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D162" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F162" s="13" t="n">
-        <v>1.566</v>
-      </c>
-    </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B163" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E163" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F163" s="13" t="n">
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="164" ht="21" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C164" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D164" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E164" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F164" s="13" t="n">
-        <v>0.141</v>
       </c>
     </row>
     <row r="165" ht="14" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B165" s="9" t="n">
@@ -4399,330 +4420,549 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F165" s="13" t="n">
-        <v>361.04</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B166" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F166" s="13" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+        </is>
+      </c>
+      <c r="B169" s="39" t="n"/>
+      <c r="C169" s="39" t="n"/>
+      <c r="D169" s="39" t="n"/>
+      <c r="E169" s="39" t="n"/>
+      <c r="F169" s="40" t="n"/>
+    </row>
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B171" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="n">
+        <v>260.943</v>
+      </c>
+    </row>
+    <row r="172" ht="31.5" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B172" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F172" s="13" t="n">
+        <v>1.566</v>
+      </c>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D173" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E173" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F173" s="13" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="174" ht="21" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D174" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F174" s="13" t="n">
+        <v>0.141</v>
+      </c>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>Çevre düzenlemesi ve çit işleri</t>
+        </is>
+      </c>
+      <c r="B175" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="D175" s="11" t="inlineStr">
+        <is>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+        </is>
+      </c>
+      <c r="E175" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F175" s="13" t="n">
+        <v>361.04</v>
+      </c>
+    </row>
+    <row r="176" ht="21" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
           <t>Kanalizasyon işleri</t>
         </is>
       </c>
-      <c r="B166" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C166" s="10" t="inlineStr">
+      <c r="B176" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
         <is>
           <t>43.527.1001</t>
         </is>
       </c>
-      <c r="D166" s="11" t="inlineStr">
+      <c r="D176" s="11" t="inlineStr">
         <is>
           <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
-      <c r="E166" s="12" t="inlineStr">
+      <c r="E176" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F166" s="13" t="n">
+      <c r="F176" s="13" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="167" ht="14" customHeight="1">
-      <c r="A167" s="15" t="n"/>
-      <c r="B167" s="9" t="n">
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="15" t="n"/>
+      <c r="B177" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C167" s="10" t="inlineStr">
+      <c r="C177" s="10" t="inlineStr">
         <is>
           <t>15.560.1003</t>
         </is>
       </c>
-      <c r="D167" s="11" t="inlineStr">
+      <c r="D177" s="11" t="inlineStr">
         <is>
           <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
-      <c r="E167" s="12" t="inlineStr">
+      <c r="E177" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F167" s="13" t="n">
+      <c r="F177" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="168" ht="21" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+    <row r="178" ht="21" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B168" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C168" s="10" t="inlineStr">
-        <is>
-          <t>30.100.1104</t>
-        </is>
-      </c>
-      <c r="D168" s="11" t="inlineStr">
+      <c r="B178" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>35.100.1104</t>
+        </is>
+      </c>
+      <c r="D178" s="11" t="inlineStr">
         <is>
           <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E168" s="12" t="inlineStr">
+      <c r="E178" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F168" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" ht="21" customHeight="1">
-      <c r="A169" s="14" t="n"/>
-      <c r="B169" s="9" t="n">
+      <c r="F178" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" ht="21" customHeight="1">
+      <c r="A179" s="14" t="n"/>
+      <c r="B179" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C169" s="10" t="inlineStr">
-        <is>
-          <t>30.100.2106</t>
-        </is>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>35.100.2106</t>
+        </is>
+      </c>
+      <c r="D179" s="11" t="inlineStr">
         <is>
           <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E169" s="12" t="inlineStr">
+      <c r="E179" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F169" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" ht="21" customHeight="1">
-      <c r="A170" s="14" t="n"/>
-      <c r="B170" s="9" t="n">
+      <c r="F179" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" ht="21" customHeight="1">
+      <c r="A180" s="14" t="n"/>
+      <c r="B180" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C170" s="10" t="inlineStr">
-        <is>
-          <t>30.135.3201</t>
-        </is>
-      </c>
-      <c r="D170" s="11" t="inlineStr">
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>35.135.3201</t>
+        </is>
+      </c>
+      <c r="D180" s="11" t="inlineStr">
         <is>
           <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E170" s="12" t="inlineStr">
+      <c r="E180" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F170" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" ht="21" customHeight="1">
-      <c r="A171" s="14" t="n"/>
-      <c r="B171" s="9" t="n">
+      <c r="F180" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" ht="21" customHeight="1">
+      <c r="A181" s="14" t="n"/>
+      <c r="B181" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C171" s="10" t="inlineStr">
-        <is>
-          <t>30.110.1104</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>35.110.1104</t>
+        </is>
+      </c>
+      <c r="D181" s="11" t="inlineStr">
         <is>
           <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E171" s="12" t="inlineStr">
+      <c r="E181" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F171" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="14" t="n"/>
-      <c r="B172" s="9" t="n">
+      <c r="F181" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="14" t="n"/>
+      <c r="B182" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C172" s="10" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="D172" s="11" t="inlineStr">
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>35.115.1003</t>
+        </is>
+      </c>
+      <c r="D182" s="11" t="inlineStr">
         <is>
           <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E172" s="12" t="inlineStr">
+      <c r="E182" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F172" s="13" t="n">
+      <c r="F182" s="13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="173" ht="21" customHeight="1">
-      <c r="A173" s="14" t="n"/>
-      <c r="B173" s="9" t="n">
+    <row r="183" ht="21" customHeight="1">
+      <c r="A183" s="14" t="n"/>
+      <c r="B183" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="C173" s="10" t="inlineStr">
-        <is>
-          <t>30.140.3105</t>
-        </is>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>35.140.3105</t>
+        </is>
+      </c>
+      <c r="D183" s="11" t="inlineStr">
         <is>
           <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E173" s="12" t="inlineStr">
+      <c r="E183" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F173" s="13" t="n">
+      <c r="F183" s="13" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="174" ht="21" customHeight="1">
-      <c r="A174" s="14" t="n"/>
-      <c r="B174" s="9" t="n">
+    <row r="184" ht="21" customHeight="1">
+      <c r="A184" s="14" t="n"/>
+      <c r="B184" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="C174" s="10" t="inlineStr">
-        <is>
-          <t>30.140.3101</t>
-        </is>
-      </c>
-      <c r="D174" s="11" t="inlineStr">
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>35.140.3101</t>
+        </is>
+      </c>
+      <c r="D184" s="11" t="inlineStr">
         <is>
           <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E174" s="12" t="inlineStr">
+      <c r="E184" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F174" s="13" t="n">
+      <c r="F184" s="13" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="175" ht="21" customHeight="1">
-      <c r="A175" s="14" t="n"/>
-      <c r="B175" s="9" t="n">
+    <row r="185" ht="21" customHeight="1">
+      <c r="A185" s="14" t="n"/>
+      <c r="B185" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C175" s="10" t="inlineStr">
-        <is>
-          <t>30.172.1706</t>
-        </is>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>35.172.1706</t>
+        </is>
+      </c>
+      <c r="D185" s="11" t="inlineStr">
         <is>
           <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E175" s="12" t="inlineStr">
+      <c r="E185" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F175" s="13" t="n">
+      <c r="F185" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="176" ht="14" customHeight="1">
-      <c r="A176" s="15" t="n"/>
-      <c r="B176" s="9" t="n">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="15" t="n"/>
+      <c r="B186" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="C176" s="10" t="inlineStr">
-        <is>
-          <t>30.170.4002</t>
-        </is>
-      </c>
-      <c r="D176" s="11" t="inlineStr">
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>35.170.4002</t>
+        </is>
+      </c>
+      <c r="D186" s="11" t="inlineStr">
         <is>
           <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
-      <c r="E176" s="12" t="inlineStr">
+      <c r="E186" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F176" s="13" t="n">
+      <c r="F186" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="17" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="17" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B178" s="39" t="n"/>
-      <c r="C178" s="39" t="n"/>
-      <c r="D178" s="39" t="n"/>
-      <c r="E178" s="39" t="n"/>
-      <c r="F178" s="40" t="n"/>
-    </row>
-    <row r="179" ht="13" customHeight="1">
-      <c r="A179" s="18" t="inlineStr">
+      <c r="B188" s="39" t="n"/>
+      <c r="C188" s="39" t="n"/>
+      <c r="D188" s="39" t="n"/>
+      <c r="E188" s="39" t="n"/>
+      <c r="F188" s="40" t="n"/>
+    </row>
+    <row r="189" ht="13" customHeight="1">
+      <c r="A189" s="18" t="inlineStr">
         <is>
           <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="18" t="inlineStr">
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="18" t="inlineStr">
         <is>
           <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="13" customHeight="1">
-      <c r="A181" s="18" t="inlineStr">
+    <row r="191" ht="13" customHeight="1">
+      <c r="A191" s="18" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="13" customHeight="1">
-      <c r="A182" s="18" t="inlineStr">
+    <row r="192" ht="13" customHeight="1">
+      <c r="A192" s="18" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
@@ -4731,96 +4971,96 @@
   </sheetData>
   <mergeCells count="91">
     <mergeCell ref="A147"/>
+    <mergeCell ref="A133:F133"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A189:F189"/>
     <mergeCell ref="A156"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A165"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
     <mergeCell ref="A155"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A130"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A148"/>
     <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A157"/>
     <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A86:A111"/>
     <mergeCell ref="A138"/>
     <mergeCell ref="A119"/>
-    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A174"/>
+    <mergeCell ref="A84"/>
     <mergeCell ref="A118"/>
-    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A178:A186"/>
+    <mergeCell ref="A175"/>
+    <mergeCell ref="A124:F124"/>
     <mergeCell ref="A144"/>
-    <mergeCell ref="A166:A167"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A106"/>
-    <mergeCell ref="A134"/>
-    <mergeCell ref="A152"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A161"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A31"/>
-    <mergeCell ref="A58"/>
+    <mergeCell ref="A151:F151"/>
     <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A64"/>
+    <mergeCell ref="A188:F188"/>
     <mergeCell ref="A141:F141"/>
-    <mergeCell ref="A107"/>
-    <mergeCell ref="A60"/>
-    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A190:F190"/>
     <mergeCell ref="A146"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A108"/>
+    <mergeCell ref="A172"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A32:A52"/>
-    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A191:F191"/>
     <mergeCell ref="A163"/>
-    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A85"/>
+    <mergeCell ref="A71:A73"/>
     <mergeCell ref="A126"/>
-    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A135"/>
+    <mergeCell ref="A62"/>
     <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A125"/>
-    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A80:A81"/>
     <mergeCell ref="A127"/>
     <mergeCell ref="A30"/>
-    <mergeCell ref="A181:F181"/>
-    <mergeCell ref="A59"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A79"/>
+    <mergeCell ref="A120:A121"/>
     <mergeCell ref="A153"/>
     <mergeCell ref="A162"/>
     <mergeCell ref="A137"/>
-    <mergeCell ref="A61:A63"/>
     <mergeCell ref="A164"/>
     <mergeCell ref="A145"/>
+    <mergeCell ref="A139"/>
     <mergeCell ref="A154"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A168:F168"/>
     <mergeCell ref="A129"/>
-    <mergeCell ref="A81:A101"/>
     <mergeCell ref="A116"/>
     <mergeCell ref="A8"/>
-    <mergeCell ref="A109"/>
-    <mergeCell ref="A168:A176"/>
+    <mergeCell ref="A171"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A63"/>
     <mergeCell ref="A10"/>
-    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A192:F192"/>
     <mergeCell ref="A117"/>
+    <mergeCell ref="A173"/>
     <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A75:A76"/>
     <mergeCell ref="A9"/>
-    <mergeCell ref="A143"/>
+    <mergeCell ref="A166"/>
+    <mergeCell ref="A77:A79"/>
     <mergeCell ref="A11"/>
+    <mergeCell ref="A32:A57"/>
+    <mergeCell ref="A65"/>
     <mergeCell ref="A128"/>
-    <mergeCell ref="A80"/>
     <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A120"/>
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A136"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A132:F132"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A57"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A176:A177"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
+++ b/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1628,28 +1628,28 @@
         <v>186</v>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="21" customHeight="1">
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>35.750.3002 (montaj)</t>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -1659,21 +1659,21 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -1681,14 +1681,14 @@
       <c r="B45" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>35.750.1502 (montaj)</t>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
@@ -1700,28 +1700,28 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" ht="21" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="14" t="n"/>
       <c r="B46" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
@@ -1729,23 +1729,23 @@
       <c r="B47" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>35.750.2001 (montaj)</t>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -1755,406 +1755,414 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>35.740.1106</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="49" ht="31.5" customHeight="1">
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="9" t="n">
         <v>18</v>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>35.740.1106 (montaj)</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" ht="14" customHeight="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
       <c r="A50" s="14" t="n"/>
       <c r="B50" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" ht="14" customHeight="1">
+        <v>361.2</v>
+      </c>
+    </row>
+    <row r="51" ht="21" customHeight="1">
       <c r="A51" s="14" t="n"/>
       <c r="B51" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>35.740.5406 (montaj)</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="14" t="n"/>
+        <v>361.2</v>
+      </c>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="15" t="n"/>
       <c r="B52" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>35.120.2016</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" ht="21" customHeight="1">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E53" s="12" t="inlineStr">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Kümes B Blok &gt;   —   inşaat alanı 1.106.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>A blok ile geometrik olarak birebir aynıdır.</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="n"/>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="40" t="n"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>1684.385</v>
+      </c>
+    </row>
+    <row r="58" ht="31.5" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>31.429</v>
+      </c>
+    </row>
+    <row r="59" ht="31.5" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>278.34</v>
+      </c>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>551.26</v>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>7.288</v>
+      </c>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1002</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>3.637</v>
+      </c>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Çelik yapım-imalat işleri</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>15.165.1003</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>44.048</v>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1202</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F53" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="54" ht="31.5" customHeight="1">
-      <c r="A54" s="14" t="n"/>
-      <c r="B54" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="55" ht="21" customHeight="1">
-      <c r="A55" s="14" t="n"/>
-      <c r="B55" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="14" t="n"/>
-      <c r="B56" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="15" t="n"/>
-      <c r="B57" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F57" s="13" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Kümes B Blok &gt;   —   inşaat alanı 1.106.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>A blok ile geometrik olarak birebir aynıdır.</t>
-        </is>
-      </c>
-      <c r="B60" s="39" t="n"/>
-      <c r="C60" s="39" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="39" t="n"/>
-      <c r="F60" s="40" t="n"/>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1001</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>1684.385</v>
-      </c>
-    </row>
-    <row r="63" ht="31.5" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="n">
-        <v>31.429</v>
-      </c>
-    </row>
-    <row r="64" ht="31.5" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="n">
-        <v>278.34</v>
-      </c>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="F65" s="13" t="n">
-        <v>551.26</v>
+        <v>674</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B66" s="9" t="n">
@@ -2162,75 +2170,75 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="67" ht="21" customHeight="1">
+        <v>507.91</v>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
       <c r="A67" s="14" t="n"/>
       <c r="B67" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>7.288</v>
-      </c>
-    </row>
-    <row r="68" ht="14" customHeight="1">
+        <v>49.85</v>
+      </c>
+    </row>
+    <row r="68" ht="21" customHeight="1">
       <c r="A68" s="15" t="n"/>
       <c r="B68" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>3.637</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B69" s="9" t="n">
@@ -2238,36 +2246,36 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>44.048</v>
+        <v>1204.98</v>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="15" t="n"/>
+      <c r="A70" s="14" t="n"/>
       <c r="B70" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
@@ -2276,165 +2284,165 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="71" ht="21" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>Tuğla ve duvar işleri</t>
-        </is>
-      </c>
+        <v>319.2</v>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="15" t="n"/>
       <c r="B71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0151</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F71" s="13" t="n">
-        <v>507.91</v>
-      </c>
-    </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="14" t="n"/>
-      <c r="B72" s="9" t="n">
+      <c r="F72" s="13" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="14" t="n"/>
+      <c r="B73" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>15.225.1410</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F72" s="13" t="n">
-        <v>49.85</v>
-      </c>
-    </row>
-    <row r="73" ht="21" customHeight="1">
-      <c r="A73" s="15" t="n"/>
-      <c r="B73" s="9" t="n">
+      <c r="F73" s="13" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="A74" s="15" t="n"/>
+      <c r="B74" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>15.225.1004</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1002</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>54.315</v>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>15.275.1116</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F73" s="13" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="74" ht="21" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Çatı ve sundurma işleri</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="n">
-        <v>1204.98</v>
-      </c>
-    </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="14" t="n"/>
-      <c r="B75" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
       <c r="F75" s="13" t="n">
-        <v>319.2</v>
+        <v>557.76</v>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="15" t="n"/>
       <c r="B76" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>51.2</v>
+        <v>647.76</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B77" s="9" t="n">
@@ -2442,12 +2450,12 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -2456,22 +2464,22 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>13.4</v>
+        <v>557.76</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="14" t="n"/>
+      <c r="A78" s="15" t="n"/>
       <c r="B78" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
@@ -2480,282 +2488,274 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="15" t="n"/>
+        <v>612.76</v>
+      </c>
+    </row>
+    <row r="79" ht="31.5" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+        </is>
+      </c>
       <c r="B79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0177</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" ht="21" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>35.100.2105</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="21" customHeight="1">
+      <c r="A82" s="14" t="n"/>
+      <c r="B82" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>35.110.1102</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="14" t="n"/>
+      <c r="B83" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>15.550.1002</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>54.315</v>
-      </c>
-    </row>
-    <row r="80" ht="14" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>15.275.1116</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="n">
-        <v>557.76</v>
-      </c>
-    </row>
-    <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="15" t="n"/>
-      <c r="B81" s="9" t="n">
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>35.115.1003</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>15.275.1117</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>647.76</v>
-      </c>
-    </row>
-    <row r="82" ht="21" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
-        <is>
-          <t>Boya, badana ve cila işleri</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>15.540.1606</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>557.76</v>
-      </c>
-    </row>
-    <row r="83" ht="21" customHeight="1">
-      <c r="A83" s="15" t="n"/>
-      <c r="B83" s="9" t="n">
+    </row>
+    <row r="84" ht="21" customHeight="1">
+      <c r="A84" s="14" t="n"/>
+      <c r="B84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>35.140.3104</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" s="14" t="n"/>
+      <c r="B85" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>35.170.1602</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" ht="21" customHeight="1">
+      <c r="A86" s="14" t="n"/>
+      <c r="B86" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>35.170.1601</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>15.540.1537</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F83" s="13" t="n">
-        <v>612.76</v>
-      </c>
-    </row>
-    <row r="84" ht="31.5" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="85" ht="21" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86" ht="21" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>35.100.2105</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" ht="21" customHeight="1">
+    </row>
+    <row r="87" ht="14" customHeight="1">
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>35.110.1102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="14" t="n"/>
       <c r="B89" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>35.140.3104</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -2764,94 +2764,94 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="14" t="n"/>
       <c r="B90" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>35.170.1602</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="14" t="n"/>
       <c r="B91" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>35.170.1601</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" ht="14" customHeight="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="92" ht="21" customHeight="1">
       <c r="A92" s="14" t="n"/>
       <c r="B92" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>35.160.6102</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="93" ht="14" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
       <c r="A93" s="14" t="n"/>
       <c r="B93" s="9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>35.150.1402</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
@@ -2860,452 +2860,427 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>2000</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
       <c r="A94" s="14" t="n"/>
       <c r="B94" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>35.150.1401</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="95" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
       <c r="A95" s="14" t="n"/>
       <c r="B95" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>35.140.1105</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" ht="14" customHeight="1">
       <c r="A96" s="14" t="n"/>
       <c r="B96" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>35.750.3002</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="97" ht="14" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" ht="21" customHeight="1">
       <c r="A97" s="14" t="n"/>
       <c r="B97" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>35.750.3002 (montaj)</t>
+        <v>17</v>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="98" ht="21" customHeight="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="98" ht="31.5" customHeight="1">
       <c r="A98" s="14" t="n"/>
       <c r="B98" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="C98" s="10" t="inlineStr">
-        <is>
-          <t>35.750.1502</t>
+        <v>18</v>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
       <c r="A99" s="14" t="n"/>
       <c r="B99" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>35.750.1502 (montaj)</t>
+        <v>19</v>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
       <c r="A100" s="14" t="n"/>
       <c r="B100" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>35.750.2001</t>
+        <v>20</v>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>361.2</v>
+      </c>
+    </row>
+    <row r="101" ht="21" customHeight="1">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1304</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F100" s="13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" ht="14" customHeight="1">
-      <c r="A101" s="14" t="n"/>
-      <c r="B101" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>35.750.2001 (montaj)</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
       <c r="F101" s="13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" ht="21" customHeight="1">
-      <c r="A102" s="14" t="n"/>
-      <c r="B102" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>35.740.1106</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F102" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" ht="21" customHeight="1">
-      <c r="A103" s="14" t="n"/>
-      <c r="B103" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>35.740.1106 (montaj)</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F103" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" ht="14" customHeight="1">
-      <c r="A104" s="14" t="n"/>
-      <c r="B104" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
-        <is>
-          <t>35.740.5406</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F104" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" ht="14" customHeight="1">
-      <c r="A105" s="14" t="n"/>
-      <c r="B105" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>35.740.5406 (montaj)</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F105" s="13" t="n">
-        <v>1</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Gübre Çukuru &gt;   —   inşaat alanı 115.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
+        </is>
+      </c>
+      <c r="B104" s="39" t="n"/>
+      <c r="C104" s="39" t="n"/>
+      <c r="D104" s="39" t="n"/>
+      <c r="E104" s="39" t="n"/>
+      <c r="F104" s="40" t="n"/>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="14" t="n"/>
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
       <c r="B106" s="9" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>35.120.2016</t>
+          <t>15.120.1101</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" ht="21" customHeight="1">
-      <c r="A107" s="14" t="n"/>
+        <v>542.7</v>
+      </c>
+    </row>
+    <row r="107" ht="31.5" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
       <c r="B107" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>502</v>
+        <v>11.934</v>
       </c>
     </row>
     <row r="108" ht="31.5" customHeight="1">
-      <c r="A108" s="14" t="n"/>
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
       <c r="B108" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+        <v>1</v>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="109" ht="21" customHeight="1">
-      <c r="A109" s="14" t="n"/>
+        <v>93.19</v>
+      </c>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
       <c r="B109" s="9" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>361.2</v>
+        <v>363.26</v>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
-      <c r="A110" s="14" t="n"/>
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
       <c r="B110" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
+        <v>1</v>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>361.2</v>
+        <v>7.599</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
       <c r="A111" s="15" t="n"/>
       <c r="B111" s="9" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>35.190.1304</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>123</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>&lt; Gübre Çukuru &gt;   —   inşaat alanı 115.00 m²</t>
+          <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
         </is>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
+          <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
         </is>
       </c>
       <c r="B114" s="39" t="n"/>
@@ -3371,7 +3346,7 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>542.7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="117" ht="31.5" customHeight="1">
@@ -3399,7 +3374,7 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>11.934</v>
+        <v>1.984</v>
       </c>
     </row>
     <row r="118" ht="31.5" customHeight="1">
@@ -3427,7 +3402,7 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>93.19</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
@@ -3455,7 +3430,7 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>363.26</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -3483,88 +3458,92 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>7.599</v>
-      </c>
-    </row>
-    <row r="121" ht="21" customHeight="1">
-      <c r="A121" s="15" t="n"/>
-      <c r="B121" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F121" s="13" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
-        </is>
-      </c>
-      <c r="B124" s="39" t="n"/>
-      <c r="C124" s="39" t="n"/>
-      <c r="D124" s="39" t="n"/>
-      <c r="E124" s="39" t="n"/>
-      <c r="F124" s="40" t="n"/>
-    </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+        <v>1.657</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
+        </is>
+      </c>
+      <c r="B123" s="39" t="n"/>
+      <c r="C123" s="39" t="n"/>
+      <c r="D123" s="39" t="n"/>
+      <c r="E123" s="39" t="n"/>
+      <c r="F123" s="40" t="n"/>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E125" s="7" t="inlineStr">
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="14" customHeight="1">
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="126" ht="31.5" customHeight="1">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B126" s="9" t="n">
@@ -3572,12 +3551,12 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>15.120.1101</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E126" s="12" t="inlineStr">
@@ -3586,586 +3565,586 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>142</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="127" ht="31.5" customHeight="1">
       <c r="A127" s="8" t="inlineStr">
         <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>6.175</v>
+      </c>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="129" ht="21" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>0.587</v>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+        </is>
+      </c>
+      <c r="B132" s="39" t="n"/>
+      <c r="C132" s="39" t="n"/>
+      <c r="D132" s="39" t="n"/>
+      <c r="E132" s="39" t="n"/>
+      <c r="F132" s="40" t="n"/>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="14" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="n">
+        <v>48.02</v>
+      </c>
+    </row>
+    <row r="135" ht="31.5" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="B135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D135" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E127" s="12" t="inlineStr">
+      <c r="E135" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F127" s="13" t="n">
-        <v>1.984</v>
-      </c>
-    </row>
-    <row r="128" ht="31.5" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D128" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F128" s="13" t="n">
-        <v>20.85</v>
-      </c>
-    </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="n">
-        <v>127.2</v>
-      </c>
-    </row>
-    <row r="130" ht="21" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D130" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F130" s="13" t="n">
-        <v>1.657</v>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="24" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
-        </is>
-      </c>
-      <c r="B133" s="39" t="n"/>
-      <c r="C133" s="39" t="n"/>
-      <c r="D133" s="39" t="n"/>
-      <c r="E133" s="39" t="n"/>
-      <c r="F133" s="40" t="n"/>
-    </row>
-    <row r="134" ht="28" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C134" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E134" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="14" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F135" s="13" t="n">
-        <v>48.8</v>
+        <v>1.922</v>
       </c>
     </row>
     <row r="136" ht="31.5" customHeight="1">
       <c r="A136" s="8" t="inlineStr">
         <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="138" ht="21" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>0.757</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="24" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
+        </is>
+      </c>
+      <c r="B141" s="39" t="n"/>
+      <c r="C141" s="39" t="n"/>
+      <c r="D141" s="39" t="n"/>
+      <c r="E141" s="39" t="n"/>
+      <c r="F141" s="40" t="n"/>
+    </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="144" ht="31.5" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="B144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D144" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E136" s="12" t="inlineStr">
+      <c r="E144" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F136" s="13" t="n">
-        <v>0.484</v>
-      </c>
-    </row>
-    <row r="137" ht="31.5" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F137" s="13" t="n">
-        <v>6.175</v>
-      </c>
-    </row>
-    <row r="138" ht="14" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F138" s="13" t="n">
-        <v>41.4</v>
-      </c>
-    </row>
-    <row r="139" ht="21" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F139" s="13" t="n">
-        <v>0.587</v>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="24" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
-        </is>
-      </c>
-      <c r="B142" s="39" t="n"/>
-      <c r="C142" s="39" t="n"/>
-      <c r="D142" s="39" t="n"/>
-      <c r="E142" s="39" t="n"/>
-      <c r="F142" s="40" t="n"/>
-    </row>
-    <row r="143" ht="28" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C143" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D144" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F144" s="13" t="n">
-        <v>48.02</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="145" ht="31.5" customHeight="1">
       <c r="A145" s="8" t="inlineStr">
         <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F146" s="13" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="147" ht="21" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="n">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="24" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
+        </is>
+      </c>
+      <c r="B150" s="39" t="n"/>
+      <c r="C150" s="39" t="n"/>
+      <c r="D150" s="39" t="n"/>
+      <c r="E150" s="39" t="n"/>
+      <c r="F150" s="40" t="n"/>
+    </row>
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F152" s="13" t="n">
+        <v>88.75</v>
+      </c>
+    </row>
+    <row r="153" ht="31.5" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
+      <c r="B153" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D145" s="11" t="inlineStr">
+      <c r="D153" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="E153" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F145" s="13" t="n">
-        <v>1.922</v>
-      </c>
-    </row>
-    <row r="146" ht="31.5" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D146" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F146" s="13" t="n">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F147" s="13" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="148" ht="21" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F148" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="24" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
-        </is>
-      </c>
-      <c r="B151" s="39" t="n"/>
-      <c r="C151" s="39" t="n"/>
-      <c r="D151" s="39" t="n"/>
-      <c r="E151" s="39" t="n"/>
-      <c r="F151" s="40" t="n"/>
-    </row>
-    <row r="152" ht="28" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="14" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F153" s="13" t="n">
-        <v>106.5</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="154" ht="31.5" customHeight="1">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B154" s="9" t="n">
@@ -4173,12 +4152,12 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
@@ -4187,232 +4166,232 @@
         </is>
       </c>
       <c r="F154" s="13" t="n">
-        <v>1.344</v>
-      </c>
-    </row>
-    <row r="155" ht="31.5" customHeight="1">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="155" ht="14" customHeight="1">
       <c r="A155" s="8" t="inlineStr">
         <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B155" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F155" s="13" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="156" ht="21" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F156" s="13" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+        </is>
+      </c>
+      <c r="B159" s="39" t="n"/>
+      <c r="C159" s="39" t="n"/>
+      <c r="D159" s="39" t="n"/>
+      <c r="E159" s="39" t="n"/>
+      <c r="F159" s="40" t="n"/>
+    </row>
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B161" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F161" s="13" t="n">
+        <v>260.943</v>
+      </c>
+    </row>
+    <row r="162" ht="31.5" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
+      <c r="B162" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr">
+      <c r="D162" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E155" s="12" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F155" s="13" t="n">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="156" ht="14" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+      <c r="F162" s="13" t="n">
+        <v>1.566</v>
+      </c>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="B163" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D163" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E156" s="12" t="inlineStr">
+      <c r="E163" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F156" s="13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="157" ht="21" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
+      <c r="F163" s="13" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="164" ht="21" customHeight="1">
+      <c r="A164" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
+      <c r="B164" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D157" s="11" t="inlineStr">
+      <c r="D164" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E157" s="12" t="inlineStr">
+      <c r="E164" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F157" s="13" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="24" customHeight="1">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
-        </is>
-      </c>
-      <c r="B160" s="39" t="n"/>
-      <c r="C160" s="39" t="n"/>
-      <c r="D160" s="39" t="n"/>
-      <c r="E160" s="39" t="n"/>
-      <c r="F160" s="40" t="n"/>
-    </row>
-    <row r="161" ht="28" customHeight="1">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C161" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="14" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D162" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F162" s="13" t="n">
-        <v>88.75</v>
-      </c>
-    </row>
-    <row r="163" ht="31.5" customHeight="1">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B163" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E163" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F163" s="13" t="n">
-        <v>1.024</v>
-      </c>
-    </row>
-    <row r="164" ht="31.5" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B164" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C164" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D164" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E164" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
       <c r="F164" s="13" t="n">
-        <v>12.3</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="165" ht="14" customHeight="1">
       <c r="A165" s="8" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
       <c r="B165" s="9" t="n">
@@ -4420,27 +4399,27 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>TKDK-0091</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F165" s="13" t="n">
-        <v>79.8</v>
+        <v>361.04</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
       <c r="A166" s="8" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B166" s="9" t="n">
@@ -4448,521 +4427,302 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="24" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
-        </is>
-      </c>
-      <c r="B169" s="39" t="n"/>
-      <c r="C169" s="39" t="n"/>
-      <c r="D169" s="39" t="n"/>
-      <c r="E169" s="39" t="n"/>
-      <c r="F169" s="40" t="n"/>
-    </row>
-    <row r="170" ht="28" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C170" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="15" t="n"/>
+      <c r="B167" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>15.560.1003</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F167" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" ht="21" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B168" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>35.100.1104</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F168" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" ht="21" customHeight="1">
+      <c r="A169" s="14" t="n"/>
+      <c r="B169" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>35.100.2106</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F169" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" ht="21" customHeight="1">
+      <c r="A170" s="14" t="n"/>
+      <c r="B170" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>35.135.3201</t>
+        </is>
+      </c>
+      <c r="D170" s="11" t="inlineStr">
+        <is>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F170" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" ht="21" customHeight="1">
+      <c r="A171" s="14" t="n"/>
       <c r="B171" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F171" s="13" t="n">
-        <v>260.943</v>
-      </c>
-    </row>
-    <row r="172" ht="31.5" customHeight="1">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="14" t="n"/>
       <c r="B172" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F172" s="13" t="n">
-        <v>1.566</v>
-      </c>
-    </row>
-    <row r="173" ht="14" customHeight="1">
-      <c r="A173" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" ht="21" customHeight="1">
+      <c r="A173" s="14" t="n"/>
       <c r="B173" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F173" s="13" t="n">
-        <v>14.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174" ht="21" customHeight="1">
-      <c r="A174" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
+      <c r="A174" s="14" t="n"/>
       <c r="B174" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F174" s="13" t="n">
-        <v>0.141</v>
-      </c>
-    </row>
-    <row r="175" ht="14" customHeight="1">
-      <c r="A175" s="8" t="inlineStr">
-        <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
-        </is>
-      </c>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="175" ht="21" customHeight="1">
+      <c r="A175" s="14" t="n"/>
       <c r="B175" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F175" s="13" t="n">
-        <v>361.04</v>
-      </c>
-    </row>
-    <row r="176" ht="21" customHeight="1">
-      <c r="A176" s="8" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="15" t="n"/>
       <c r="B176" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F176" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="177" ht="14" customHeight="1">
-      <c r="A177" s="15" t="n"/>
-      <c r="B177" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C177" s="10" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E177" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F177" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="178" ht="21" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B178" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C178" s="10" t="inlineStr">
-        <is>
-          <t>35.100.1104</t>
-        </is>
-      </c>
-      <c r="D178" s="11" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E178" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F178" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" ht="21" customHeight="1">
-      <c r="A179" s="14" t="n"/>
-      <c r="B179" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C179" s="10" t="inlineStr">
-        <is>
-          <t>35.100.2106</t>
-        </is>
-      </c>
-      <c r="D179" s="11" t="inlineStr">
-        <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E179" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F179" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" ht="21" customHeight="1">
-      <c r="A180" s="14" t="n"/>
-      <c r="B180" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C180" s="10" t="inlineStr">
-        <is>
-          <t>35.135.3201</t>
-        </is>
-      </c>
-      <c r="D180" s="11" t="inlineStr">
-        <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E180" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F180" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" ht="21" customHeight="1">
-      <c r="A181" s="14" t="n"/>
-      <c r="B181" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C181" s="10" t="inlineStr">
-        <is>
-          <t>35.110.1104</t>
-        </is>
-      </c>
-      <c r="D181" s="11" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E181" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F181" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" ht="14" customHeight="1">
-      <c r="A182" s="14" t="n"/>
-      <c r="B182" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C182" s="10" t="inlineStr">
-        <is>
-          <t>35.115.1003</t>
-        </is>
-      </c>
-      <c r="D182" s="11" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E182" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F182" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183" ht="21" customHeight="1">
-      <c r="A183" s="14" t="n"/>
-      <c r="B183" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C183" s="10" t="inlineStr">
-        <is>
-          <t>35.140.3105</t>
-        </is>
-      </c>
-      <c r="D183" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E183" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F183" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="184" ht="21" customHeight="1">
-      <c r="A184" s="14" t="n"/>
-      <c r="B184" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C184" s="10" t="inlineStr">
-        <is>
-          <t>35.140.3101</t>
-        </is>
-      </c>
-      <c r="D184" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E184" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F184" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="185" ht="21" customHeight="1">
-      <c r="A185" s="14" t="n"/>
-      <c r="B185" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>35.172.1706</t>
-        </is>
-      </c>
-      <c r="D185" s="11" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E185" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F185" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="15" t="n"/>
-      <c r="B186" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C186" s="10" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="D186" s="11" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E186" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F186" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="17" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="17" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B188" s="39" t="n"/>
-      <c r="C188" s="39" t="n"/>
-      <c r="D188" s="39" t="n"/>
-      <c r="E188" s="39" t="n"/>
-      <c r="F188" s="40" t="n"/>
-    </row>
-    <row r="189" ht="13" customHeight="1">
-      <c r="A189" s="18" t="inlineStr">
+      <c r="B178" s="39" t="n"/>
+      <c r="C178" s="39" t="n"/>
+      <c r="D178" s="39" t="n"/>
+      <c r="E178" s="39" t="n"/>
+      <c r="F178" s="40" t="n"/>
+    </row>
+    <row r="179" ht="13" customHeight="1">
+      <c r="A179" s="18" t="inlineStr">
         <is>
           <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="18" t="inlineStr">
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="18" t="inlineStr">
         <is>
           <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="13" customHeight="1">
-      <c r="A191" s="18" t="inlineStr">
+    <row r="181" ht="13" customHeight="1">
+      <c r="A181" s="18" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="13" customHeight="1">
-      <c r="A192" s="18" t="inlineStr">
+    <row r="182" ht="13" customHeight="1">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
@@ -4971,96 +4731,96 @@
   </sheetData>
   <mergeCells count="91">
     <mergeCell ref="A147"/>
-    <mergeCell ref="A133:F133"/>
     <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A189:F189"/>
     <mergeCell ref="A156"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A165"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="A155"/>
-    <mergeCell ref="A160:F160"/>
-    <mergeCell ref="A130"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A148"/>
     <mergeCell ref="A150:F150"/>
-    <mergeCell ref="A157"/>
     <mergeCell ref="A159:F159"/>
-    <mergeCell ref="A86:A111"/>
     <mergeCell ref="A138"/>
     <mergeCell ref="A119"/>
-    <mergeCell ref="A174"/>
-    <mergeCell ref="A84"/>
+    <mergeCell ref="A77:A78"/>
     <mergeCell ref="A118"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A178:A186"/>
-    <mergeCell ref="A175"/>
-    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A110:A111"/>
     <mergeCell ref="A144"/>
+    <mergeCell ref="A166:A167"/>
     <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A106"/>
+    <mergeCell ref="A134"/>
+    <mergeCell ref="A152"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A161"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A31"/>
-    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A58"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A64"/>
-    <mergeCell ref="A188:F188"/>
     <mergeCell ref="A141:F141"/>
-    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="A107"/>
+    <mergeCell ref="A60"/>
+    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A146"/>
-    <mergeCell ref="A172"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="A108"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A32:A52"/>
+    <mergeCell ref="A182:F182"/>
     <mergeCell ref="A163"/>
-    <mergeCell ref="A169:F169"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A85"/>
-    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A178:F178"/>
     <mergeCell ref="A126"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A135"/>
-    <mergeCell ref="A62"/>
     <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A125"/>
+    <mergeCell ref="A179:F179"/>
     <mergeCell ref="A127"/>
     <mergeCell ref="A30"/>
-    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A59"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A79"/>
     <mergeCell ref="A153"/>
     <mergeCell ref="A162"/>
     <mergeCell ref="A137"/>
+    <mergeCell ref="A61:A63"/>
     <mergeCell ref="A164"/>
     <mergeCell ref="A145"/>
-    <mergeCell ref="A139"/>
     <mergeCell ref="A154"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A129"/>
+    <mergeCell ref="A81:A101"/>
     <mergeCell ref="A116"/>
     <mergeCell ref="A8"/>
-    <mergeCell ref="A171"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A63"/>
+    <mergeCell ref="A109"/>
+    <mergeCell ref="A168:A176"/>
     <mergeCell ref="A10"/>
-    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A117"/>
-    <mergeCell ref="A173"/>
     <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A75:A76"/>
     <mergeCell ref="A9"/>
-    <mergeCell ref="A166"/>
-    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A143"/>
     <mergeCell ref="A11"/>
-    <mergeCell ref="A32:A57"/>
-    <mergeCell ref="A65"/>
     <mergeCell ref="A128"/>
+    <mergeCell ref="A80"/>
     <mergeCell ref="A66:A68"/>
+    <mergeCell ref="A120"/>
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A136"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A132:F132"/>
     <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A57"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A64:A65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
+++ b/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
@@ -227,9 +227,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -281,6 +278,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1772,19 +1772,19 @@
         <v>502</v>
       </c>
     </row>
-    <row r="49" ht="31.5" customHeight="1">
+    <row r="49" ht="21" customHeight="1">
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
@@ -1793,136 +1793,144 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>502</v>
+        <v>361.2</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
-      <c r="A50" s="14" t="n"/>
+      <c r="A50" s="15" t="n"/>
       <c r="B50" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="51" ht="21" customHeight="1">
-      <c r="A51" s="14" t="n"/>
-      <c r="B51" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="52" ht="21" customHeight="1">
-      <c r="A52" s="15" t="n"/>
-      <c r="B52" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>&lt; Kümes B Blok &gt;   —   inşaat alanı 1.106.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>A blok ile geometrik olarak birebir aynıdır.</t>
         </is>
       </c>
-      <c r="B55" s="39" t="n"/>
-      <c r="C55" s="39" t="n"/>
-      <c r="D55" s="39" t="n"/>
-      <c r="E55" s="39" t="n"/>
-      <c r="F55" s="40" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="B53" s="39" t="n"/>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="40" t="n"/>
+    </row>
+    <row r="54" ht="28" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>1684.385</v>
+      </c>
+    </row>
+    <row r="56" ht="31.5" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>31.429</v>
+      </c>
+    </row>
+    <row r="57" ht="31.5" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B57" s="9" t="n">
@@ -1930,12 +1938,12 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
@@ -1944,13 +1952,13 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>1684.385</v>
-      </c>
-    </row>
-    <row r="58" ht="31.5" customHeight="1">
+        <v>278.34</v>
+      </c>
+    </row>
+    <row r="58" ht="14" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B58" s="9" t="n">
@@ -1958,27 +1966,27 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31.429</v>
-      </c>
-    </row>
-    <row r="59" ht="31.5" customHeight="1">
+        <v>551.26</v>
+      </c>
+    </row>
+    <row r="59" ht="21" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B59" s="9" t="n">
@@ -1986,68 +1994,60 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>278.34</v>
-      </c>
-    </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="14" t="n"/>
       <c r="B60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>551.26</v>
-      </c>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
+        <v>7.288</v>
+      </c>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="15" t="n"/>
       <c r="B61" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
@@ -2056,22 +2056,26 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>4.16</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="14" t="n"/>
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Çelik yapım-imalat işleri</t>
+        </is>
+      </c>
       <c r="B62" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
@@ -2080,37 +2084,37 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>7.288</v>
+        <v>44.048</v>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="15" t="n"/>
       <c r="B63" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>3.637</v>
+        <v>674</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B64" s="9" t="n">
@@ -2118,279 +2122,279 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>44.048</v>
+        <v>507.91</v>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="15" t="n"/>
+      <c r="A65" s="14" t="n"/>
       <c r="B65" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>49.85</v>
+      </c>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>15.225.1004</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Çatı ve sundurma işleri</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>1204.98</v>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="14" t="n"/>
+      <c r="B68" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0115</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F65" s="13" t="n">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="66" ht="21" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>Tuğla ve duvar işleri</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>15.225.1010</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="F68" s="13" t="n">
+        <v>319.2</v>
+      </c>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>15.315.1001</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0151</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F66" s="13" t="n">
-        <v>507.91</v>
-      </c>
-    </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="14" t="n"/>
-      <c r="B67" s="9" t="n">
+      <c r="F70" s="13" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="14" t="n"/>
+      <c r="B71" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>15.225.1410</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F67" s="13" t="n">
-        <v>49.85</v>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
-      <c r="A68" s="15" t="n"/>
-      <c r="B68" s="9" t="n">
+      <c r="F71" s="13" t="n">
+        <v>5.67</v>
+      </c>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="15" t="n"/>
+      <c r="B72" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>15.225.1004</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1002</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>54.315</v>
+      </c>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Sıva, alçı, derz ve şap işleri</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>15.275.1116</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F68" s="13" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" ht="21" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>Çatı ve sundurma işleri</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="n">
-        <v>1204.98</v>
-      </c>
-    </row>
-    <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="14" t="n"/>
-      <c r="B70" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="n">
-        <v>319.2</v>
-      </c>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="15" t="n"/>
-      <c r="B71" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>15.315.1001</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="n">
-        <v>51.2</v>
-      </c>
-    </row>
-    <row r="72" ht="21" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="n">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="73" ht="21" customHeight="1">
-      <c r="A73" s="14" t="n"/>
-      <c r="B73" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="F73" s="13" t="n">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="74" ht="21" customHeight="1">
+        <v>557.76</v>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
       <c r="A74" s="15" t="n"/>
       <c r="B74" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>54.315</v>
-      </c>
-    </row>
-    <row r="75" ht="14" customHeight="1">
+        <v>647.76</v>
+      </c>
+    </row>
+    <row r="75" ht="21" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B75" s="9" t="n">
@@ -2398,12 +2402,12 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
@@ -2415,19 +2419,19 @@
         <v>557.76</v>
       </c>
     </row>
-    <row r="76" ht="14" customHeight="1">
+    <row r="76" ht="21" customHeight="1">
       <c r="A76" s="15" t="n"/>
       <c r="B76" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
@@ -2436,13 +2440,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>647.76</v>
-      </c>
-    </row>
-    <row r="77" ht="21" customHeight="1">
+        <v>612.76</v>
+      </c>
+    </row>
+    <row r="77" ht="31.5" customHeight="1">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B77" s="9" t="n">
@@ -2450,12 +2454,12 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
@@ -2464,106 +2468,102 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>557.76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="15" t="n"/>
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
       <c r="B78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>35.100.2105</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
+      <c r="A80" s="14" t="n"/>
+      <c r="B80" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>15.540.1537</t>
-        </is>
-      </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="n">
-        <v>612.76</v>
-      </c>
-    </row>
-    <row r="79" ht="31.5" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>TKDK-0177</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="80" ht="21" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="81" ht="21" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="14" t="n"/>
       <c r="B81" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>35.100.2105</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -2572,46 +2572,46 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
       <c r="A82" s="14" t="n"/>
       <c r="B82" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>35.110.1102</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" ht="14" customHeight="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83" ht="21" customHeight="1">
       <c r="A83" s="14" t="n"/>
       <c r="B83" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -2620,94 +2620,94 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
       <c r="A84" s="14" t="n"/>
       <c r="B84" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>35.140.3104</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="85" ht="21" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
       <c r="A85" s="14" t="n"/>
       <c r="B85" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>35.170.1602</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" ht="21" customHeight="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
       <c r="A86" s="14" t="n"/>
       <c r="B86" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>35.170.1601</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" ht="14" customHeight="1">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="87" ht="21" customHeight="1">
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>35.160.6102</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
@@ -2716,22 +2716,22 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="88" ht="14" customHeight="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>35.150.1402</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
@@ -2740,22 +2740,22 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
       <c r="A89" s="14" t="n"/>
       <c r="B89" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>35.150.1401</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
@@ -2764,46 +2764,46 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>600</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
       <c r="A90" s="14" t="n"/>
       <c r="B90" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>35.140.1105</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
       <c r="A91" s="14" t="n"/>
       <c r="B91" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>35.750.3002</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
@@ -2812,22 +2812,22 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>186</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
       <c r="A92" s="14" t="n"/>
       <c r="B92" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
@@ -2839,43 +2839,43 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" ht="21" customHeight="1">
+    <row r="93" ht="14" customHeight="1">
       <c r="A93" s="14" t="n"/>
       <c r="B93" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" ht="14" customHeight="1">
       <c r="A94" s="14" t="n"/>
       <c r="B94" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>35.740.1106</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
@@ -2887,1399 +2887,1415 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" ht="14" customHeight="1">
+    <row r="95" ht="21" customHeight="1">
       <c r="A95" s="14" t="n"/>
       <c r="B95" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" ht="14" customHeight="1">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
       <c r="A96" s="14" t="n"/>
       <c r="B96" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>35.120.2016</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" s="14" t="n"/>
+      <c r="A97" s="15" t="n"/>
       <c r="B97" s="9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="98" ht="31.5" customHeight="1">
-      <c r="A98" s="14" t="n"/>
-      <c r="B98" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D98" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F98" s="13" t="n">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="99" ht="21" customHeight="1">
-      <c r="A99" s="14" t="n"/>
-      <c r="B99" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F99" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="100" ht="21" customHeight="1">
-      <c r="A100" s="14" t="n"/>
-      <c r="B100" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F100" s="13" t="n">
-        <v>361.2</v>
-      </c>
-    </row>
-    <row r="101" ht="21" customHeight="1">
-      <c r="A101" s="15" t="n"/>
-      <c r="B101" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="n">
         <v>123</v>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>&lt; Gübre Çukuru &gt;   —   inşaat alanı 115.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
         </is>
       </c>
-      <c r="B104" s="39" t="n"/>
-      <c r="C104" s="39" t="n"/>
-      <c r="D104" s="39" t="n"/>
-      <c r="E104" s="39" t="n"/>
-      <c r="F104" s="40" t="n"/>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="B100" s="39" t="n"/>
+      <c r="C100" s="39" t="n"/>
+      <c r="D100" s="39" t="n"/>
+      <c r="E100" s="39" t="n"/>
+      <c r="F100" s="40" t="n"/>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="14" customHeight="1">
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>542.7</v>
+      </c>
+    </row>
+    <row r="103" ht="31.5" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>11.934</v>
+      </c>
+    </row>
+    <row r="104" ht="31.5" customHeight="1">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>93.19</v>
+      </c>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>363.26</v>
+      </c>
+    </row>
+    <row r="106" ht="21" customHeight="1">
       <c r="A106" s="8" t="inlineStr">
         <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>7.599</v>
+      </c>
+    </row>
+    <row r="107" ht="21" customHeight="1">
+      <c r="A107" s="15" t="n"/>
+      <c r="B107" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="24" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
+        </is>
+      </c>
+      <c r="B110" s="39" t="n"/>
+      <c r="C110" s="39" t="n"/>
+      <c r="D110" s="39" t="n"/>
+      <c r="E110" s="39" t="n"/>
+      <c r="F110" s="40" t="n"/>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="B112" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D106" s="11" t="inlineStr">
+      <c r="D112" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E106" s="12" t="inlineStr">
+      <c r="E112" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F106" s="13" t="n">
-        <v>542.7</v>
-      </c>
-    </row>
-    <row r="107" ht="31.5" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="F112" s="13" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="113" ht="31.5" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="B113" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E107" s="12" t="inlineStr">
+      <c r="E113" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F107" s="13" t="n">
-        <v>11.934</v>
-      </c>
-    </row>
-    <row r="108" ht="31.5" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="F113" s="13" t="n">
+        <v>1.984</v>
+      </c>
+    </row>
+    <row r="114" ht="31.5" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="B114" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="D114" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="E114" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F108" s="13" t="n">
-        <v>93.19</v>
-      </c>
-    </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="F114" s="13" t="n">
+        <v>20.85</v>
+      </c>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B109" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="B115" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D109" s="11" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E109" s="12" t="inlineStr">
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F109" s="13" t="n">
-        <v>363.26</v>
-      </c>
-    </row>
-    <row r="110" ht="21" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+      <c r="F115" s="13" t="n">
+        <v>127.2</v>
+      </c>
+    </row>
+    <row r="116" ht="21" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
+      <c r="B116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="D116" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E110" s="12" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F110" s="13" t="n">
-        <v>7.599</v>
-      </c>
-    </row>
-    <row r="111" ht="21" customHeight="1">
-      <c r="A111" s="15" t="n"/>
-      <c r="B111" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
+      <c r="F116" s="13" t="n">
+        <v>1.657</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="24" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
+        </is>
+      </c>
+      <c r="B119" s="39" t="n"/>
+      <c r="C119" s="39" t="n"/>
+      <c r="D119" s="39" t="n"/>
+      <c r="E119" s="39" t="n"/>
+      <c r="F119" s="40" t="n"/>
+    </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>48.8</v>
+      </c>
+    </row>
+    <row r="122" ht="31.5" customHeight="1">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="n">
+        <v>0.484</v>
+      </c>
+    </row>
+    <row r="123" ht="31.5" customHeight="1">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>6.175</v>
+      </c>
+    </row>
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="125" ht="21" customHeight="1">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F111" s="13" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Ölü Atma Çukuru &gt;   —   inşaat alanı 18.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
-        </is>
-      </c>
-      <c r="B114" s="39" t="n"/>
-      <c r="C114" s="39" t="n"/>
-      <c r="D114" s="39" t="n"/>
-      <c r="E114" s="39" t="n"/>
-      <c r="F114" s="40" t="n"/>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="F125" s="13" t="n">
+        <v>0.587</v>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+        </is>
+      </c>
+      <c r="B128" s="39" t="n"/>
+      <c r="C128" s="39" t="n"/>
+      <c r="D128" s="39" t="n"/>
+      <c r="E128" s="39" t="n"/>
+      <c r="F128" s="40" t="n"/>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="14" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="B130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E116" s="12" t="inlineStr">
+      <c r="E130" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F116" s="13" t="n">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="117" ht="31.5" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+      <c r="F130" s="13" t="n">
+        <v>48.02</v>
+      </c>
+    </row>
+    <row r="131" ht="31.5" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="B131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr">
+      <c r="D131" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E117" s="12" t="inlineStr">
+      <c r="E131" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F117" s="13" t="n">
-        <v>1.984</v>
-      </c>
-    </row>
-    <row r="118" ht="31.5" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+      <c r="F131" s="13" t="n">
+        <v>1.922</v>
+      </c>
+    </row>
+    <row r="132" ht="31.5" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="B132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
+      <c r="D132" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E118" s="12" t="inlineStr">
+      <c r="E132" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F118" s="13" t="n">
-        <v>20.85</v>
-      </c>
-    </row>
-    <row r="119" ht="14" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="F132" s="13" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B119" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="B133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D119" s="11" t="inlineStr">
+      <c r="D133" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E119" s="12" t="inlineStr">
+      <c r="E133" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F119" s="13" t="n">
-        <v>127.2</v>
-      </c>
-    </row>
-    <row r="120" ht="21" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="F133" s="13" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="134" ht="21" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="B134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D120" s="11" t="inlineStr">
+      <c r="D134" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E120" s="12" t="inlineStr">
+      <c r="E134" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F120" s="13" t="n">
-        <v>1.657</v>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Foseptik &gt;   —   inşaat alanı 4.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
-        </is>
-      </c>
-      <c r="B123" s="39" t="n"/>
-      <c r="C123" s="39" t="n"/>
-      <c r="D123" s="39" t="n"/>
-      <c r="E123" s="39" t="n"/>
-      <c r="F123" s="40" t="n"/>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="7" t="inlineStr">
+      <c r="F134" s="13" t="n">
+        <v>0.757</v>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
+        </is>
+      </c>
+      <c r="B137" s="39" t="n"/>
+      <c r="C137" s="39" t="n"/>
+      <c r="D137" s="39" t="n"/>
+      <c r="E137" s="39" t="n"/>
+      <c r="F137" s="40" t="n"/>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B138" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
+      <c r="C138" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr">
+      <c r="D138" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="E138" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="F138" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="B139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="E139" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F125" s="13" t="n">
-        <v>48.8</v>
-      </c>
-    </row>
-    <row r="126" ht="31.5" customHeight="1">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="F139" s="13" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="140" ht="31.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="B140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E126" s="12" t="inlineStr">
+      <c r="E140" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F126" s="13" t="n">
-        <v>0.484</v>
-      </c>
-    </row>
-    <row r="127" ht="31.5" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+      <c r="F140" s="13" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="141" ht="31.5" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E127" s="12" t="inlineStr">
+      <c r="E141" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F127" s="13" t="n">
-        <v>6.175</v>
-      </c>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+      <c r="F141" s="13" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D142" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E128" s="12" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F128" s="13" t="n">
-        <v>41.4</v>
-      </c>
-    </row>
-    <row r="129" ht="21" customHeight="1">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="F142" s="13" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="143" ht="21" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="B143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D143" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E129" s="12" t="inlineStr">
+      <c r="E143" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F129" s="13" t="n">
-        <v>0.587</v>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
-        </is>
-      </c>
-      <c r="B132" s="39" t="n"/>
-      <c r="C132" s="39" t="n"/>
-      <c r="D132" s="39" t="n"/>
-      <c r="E132" s="39" t="n"/>
-      <c r="F132" s="40" t="n"/>
-    </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="7" t="inlineStr">
+      <c r="F143" s="13" t="n">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="24" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
+        </is>
+      </c>
+      <c r="B146" s="39" t="n"/>
+      <c r="C146" s="39" t="n"/>
+      <c r="D146" s="39" t="n"/>
+      <c r="E146" s="39" t="n"/>
+      <c r="F146" s="40" t="n"/>
+    </row>
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B147" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C147" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="D147" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="E147" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F133" s="7" t="inlineStr">
+      <c r="F147" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="14" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D148" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E148" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F134" s="13" t="n">
-        <v>48.02</v>
-      </c>
-    </row>
-    <row r="135" ht="31.5" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+      <c r="F148" s="13" t="n">
+        <v>88.75</v>
+      </c>
+    </row>
+    <row r="149" ht="31.5" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E135" s="12" t="inlineStr">
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F135" s="13" t="n">
-        <v>1.922</v>
-      </c>
-    </row>
-    <row r="136" ht="31.5" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="F149" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="150" ht="31.5" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D150" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E136" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F136" s="13" t="n">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+      <c r="F150" s="13" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="B151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D151" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E137" s="12" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F137" s="13" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="138" ht="21" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="F151" s="13" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="152" ht="21" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
+      <c r="B152" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D152" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E138" s="12" t="inlineStr">
+      <c r="E152" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F138" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="24" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
-        </is>
-      </c>
-      <c r="B141" s="39" t="n"/>
-      <c r="C141" s="39" t="n"/>
-      <c r="D141" s="39" t="n"/>
-      <c r="E141" s="39" t="n"/>
-      <c r="F141" s="40" t="n"/>
-    </row>
-    <row r="142" ht="28" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
+      <c r="F152" s="13" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="24" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+        </is>
+      </c>
+      <c r="B155" s="39" t="n"/>
+      <c r="C155" s="39" t="n"/>
+      <c r="D155" s="39" t="n"/>
+      <c r="E155" s="39" t="n"/>
+      <c r="F155" s="40" t="n"/>
+    </row>
+    <row r="156" ht="28" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B156" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C156" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="D156" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="E156" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
+      <c r="F156" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D143" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="B157" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F143" s="13" t="n">
-        <v>106.5</v>
-      </c>
-    </row>
-    <row r="144" ht="31.5" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D144" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E144" s="12" t="inlineStr">
+      <c r="F157" s="13" t="n">
+        <v>260.943</v>
+      </c>
+    </row>
+    <row r="158" ht="31.5" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F144" s="13" t="n">
-        <v>1.344</v>
-      </c>
-    </row>
-    <row r="145" ht="31.5" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F145" s="13" t="n">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="F158" s="13" t="n">
+        <v>1.566</v>
+      </c>
+    </row>
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="B159" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D159" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F146" s="13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="147" ht="21" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
+      <c r="F159" s="13" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="160" ht="21" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
+      <c r="B160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D147" s="11" t="inlineStr">
+      <c r="D160" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E147" s="12" t="inlineStr">
+      <c r="E160" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F147" s="13" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
-        </is>
-      </c>
-      <c r="B150" s="39" t="n"/>
-      <c r="C150" s="39" t="n"/>
-      <c r="D150" s="39" t="n"/>
-      <c r="E150" s="39" t="n"/>
-      <c r="F150" s="40" t="n"/>
-    </row>
-    <row r="151" ht="28" customHeight="1">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F152" s="13" t="n">
-        <v>88.75</v>
-      </c>
-    </row>
-    <row r="153" ht="31.5" customHeight="1">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F153" s="13" t="n">
-        <v>1.024</v>
-      </c>
-    </row>
-    <row r="154" ht="31.5" customHeight="1">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D154" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E154" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F154" s="13" t="n">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F155" s="13" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="156" ht="21" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D156" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E156" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F156" s="13" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
-        </is>
-      </c>
-      <c r="B159" s="39" t="n"/>
-      <c r="C159" s="39" t="n"/>
-      <c r="D159" s="39" t="n"/>
-      <c r="E159" s="39" t="n"/>
-      <c r="F159" s="40" t="n"/>
-    </row>
-    <row r="160" ht="28" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D160" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
+      <c r="F160" s="13" t="n">
+        <v>0.141</v>
       </c>
     </row>
     <row r="161" ht="14" customHeight="1">
       <c r="A161" s="8" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
       <c r="B161" s="9" t="n">
@@ -4287,27 +4303,27 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>TKDK-0091</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>260.943</v>
-      </c>
-    </row>
-    <row r="162" ht="31.5" customHeight="1">
+        <v>361.04</v>
+      </c>
+    </row>
+    <row r="162" ht="21" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B162" s="9" t="n">
@@ -4315,55 +4331,51 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>1.566</v>
+        <v>50</v>
       </c>
     </row>
     <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
+      <c r="A163" s="15" t="n"/>
       <c r="B163" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F163" s="13" t="n">
-        <v>14.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
       <c r="A164" s="8" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B164" s="9" t="n">
@@ -4371,358 +4383,250 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>35.100.1104</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F164" s="13" t="n">
-        <v>0.141</v>
-      </c>
-    </row>
-    <row r="165" ht="14" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" ht="21" customHeight="1">
+      <c r="A165" s="14" t="n"/>
       <c r="B165" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F165" s="13" t="n">
-        <v>361.04</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
+      <c r="A166" s="14" t="n"/>
       <c r="B166" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="167" ht="14" customHeight="1">
-      <c r="A167" s="15" t="n"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" ht="21" customHeight="1">
+      <c r="A167" s="14" t="n"/>
       <c r="B167" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>35.110.1104</t>
+        </is>
+      </c>
+      <c r="D167" s="11" t="inlineStr">
+        <is>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E167" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F167" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="14" t="n"/>
+      <c r="B168" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>35.115.1003</t>
+        </is>
+      </c>
+      <c r="D168" s="11" t="inlineStr">
+        <is>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F168" s="13" t="n">
         <v>2</v>
-      </c>
-      <c r="C167" s="10" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E167" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F167" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="168" ht="21" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B168" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C168" s="10" t="inlineStr">
-        <is>
-          <t>35.100.1104</t>
-        </is>
-      </c>
-      <c r="D168" s="11" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E168" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F168" s="13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>35.100.2106</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F169" s="13" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1">
       <c r="A170" s="14" t="n"/>
       <c r="B170" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F170" s="13" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1">
       <c r="A171" s="14" t="n"/>
       <c r="B171" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>35.172.1706</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C171" s="10" t="inlineStr">
-        <is>
-          <t>35.110.1104</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="15" t="n"/>
+      <c r="B172" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>35.170.4002</t>
+        </is>
+      </c>
+      <c r="D172" s="11" t="inlineStr">
+        <is>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F171" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="14" t="n"/>
-      <c r="B172" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C172" s="10" t="inlineStr">
-        <is>
-          <t>35.115.1003</t>
-        </is>
-      </c>
-      <c r="D172" s="11" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E172" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
       <c r="F172" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" ht="21" customHeight="1">
-      <c r="A173" s="14" t="n"/>
-      <c r="B173" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C173" s="10" t="inlineStr">
-        <is>
-          <t>35.140.3105</t>
-        </is>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E173" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F173" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="174" ht="21" customHeight="1">
-      <c r="A174" s="14" t="n"/>
-      <c r="B174" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C174" s="10" t="inlineStr">
-        <is>
-          <t>35.140.3101</t>
-        </is>
-      </c>
-      <c r="D174" s="11" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E174" s="12" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F174" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="175" ht="21" customHeight="1">
-      <c r="A175" s="14" t="n"/>
-      <c r="B175" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C175" s="10" t="inlineStr">
-        <is>
-          <t>35.172.1706</t>
-        </is>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E175" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F175" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="176" ht="14" customHeight="1">
-      <c r="A176" s="15" t="n"/>
-      <c r="B176" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C176" s="10" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="D176" s="11" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E176" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F176" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="178">
+    <row r="174">
+      <c r="A174" s="16" t="inlineStr">
+        <is>
+          <t>AÇIKLAMALAR</t>
+        </is>
+      </c>
+      <c r="B174" s="39" t="n"/>
+      <c r="C174" s="39" t="n"/>
+      <c r="D174" s="39" t="n"/>
+      <c r="E174" s="39" t="n"/>
+      <c r="F174" s="40" t="n"/>
+    </row>
+    <row r="175" ht="13" customHeight="1">
+      <c r="A175" s="17" t="inlineStr">
+        <is>
+          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="17" t="inlineStr">
+        <is>
+          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="13" customHeight="1">
+      <c r="A177" s="17" t="inlineStr">
+        <is>
+          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="13" customHeight="1">
       <c r="A178" s="17" t="inlineStr">
-        <is>
-          <t>AÇIKLAMALAR</t>
-        </is>
-      </c>
-      <c r="B178" s="39" t="n"/>
-      <c r="C178" s="39" t="n"/>
-      <c r="D178" s="39" t="n"/>
-      <c r="E178" s="39" t="n"/>
-      <c r="F178" s="40" t="n"/>
-    </row>
-    <row r="179" ht="13" customHeight="1">
-      <c r="A179" s="18" t="inlineStr">
-        <is>
-          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="18" t="inlineStr">
-        <is>
-          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="13" customHeight="1">
-      <c r="A181" s="18" t="inlineStr">
-        <is>
-          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="13" customHeight="1">
-      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
@@ -4730,97 +4634,97 @@
     </row>
   </sheetData>
   <mergeCells count="91">
-    <mergeCell ref="A147"/>
+    <mergeCell ref="A174:F174"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A156"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="A165"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A155"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A130"/>
+    <mergeCell ref="A77"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A150:F150"/>
-    <mergeCell ref="A159:F159"/>
-    <mergeCell ref="A138"/>
-    <mergeCell ref="A119"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A118"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A144"/>
-    <mergeCell ref="A166:A167"/>
+    <mergeCell ref="A148"/>
+    <mergeCell ref="A157"/>
+    <mergeCell ref="A123"/>
+    <mergeCell ref="A132"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A133"/>
+    <mergeCell ref="A158"/>
+    <mergeCell ref="A55"/>
+    <mergeCell ref="A104"/>
+    <mergeCell ref="A160"/>
+    <mergeCell ref="A150"/>
+    <mergeCell ref="A159"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A106"/>
+    <mergeCell ref="A99:F99"/>
     <mergeCell ref="A134"/>
     <mergeCell ref="A152"/>
-    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A121"/>
+    <mergeCell ref="A164:A172"/>
     <mergeCell ref="A161"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A31"/>
     <mergeCell ref="A58"/>
+    <mergeCell ref="A79:A97"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A141:F141"/>
-    <mergeCell ref="A107"/>
-    <mergeCell ref="A60"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="A146"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A108"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A32:A52"/>
-    <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A163"/>
+    <mergeCell ref="A124"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A149"/>
     <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A126"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A135"/>
+    <mergeCell ref="A151"/>
+    <mergeCell ref="A141"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A122"/>
     <mergeCell ref="A125"/>
-    <mergeCell ref="A179:F179"/>
-    <mergeCell ref="A127"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A112"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A59:A61"/>
     <mergeCell ref="A30"/>
-    <mergeCell ref="A181:F181"/>
-    <mergeCell ref="A59"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A79"/>
-    <mergeCell ref="A153"/>
-    <mergeCell ref="A162"/>
-    <mergeCell ref="A137"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A164"/>
-    <mergeCell ref="A145"/>
-    <mergeCell ref="A154"/>
+    <mergeCell ref="A114"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A56"/>
+    <mergeCell ref="A139"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A129"/>
-    <mergeCell ref="A81:A101"/>
     <mergeCell ref="A116"/>
     <mergeCell ref="A8"/>
-    <mergeCell ref="A109"/>
-    <mergeCell ref="A168:A176"/>
+    <mergeCell ref="A131"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A140"/>
     <mergeCell ref="A10"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A117"/>
-    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A115"/>
+    <mergeCell ref="A102"/>
     <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A67:A69"/>
     <mergeCell ref="A9"/>
     <mergeCell ref="A143"/>
+    <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
-    <mergeCell ref="A128"/>
-    <mergeCell ref="A80"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="A120"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="A136"/>
+    <mergeCell ref="A103"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A78"/>
+    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A32:A50"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A105"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A146:F146"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A57"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A113"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A119:F119"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
+++ b/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
@@ -649,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F178"/>
+  <dimension ref="A1:F176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3375,7 +3375,7 @@
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Dış ölçü 2,00 x 2,00 m, betonarme sızdırmaz.</t>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı, 6 m³; kazı ve grobeton oturma yatağı üzerine yerleştirilir (çukur dış ölçüsü 2,00 x 2,00 m).</t>
         </is>
       </c>
       <c r="B119" s="39" t="n"/>
@@ -3472,718 +3472,718 @@
         <v>0.484</v>
       </c>
     </row>
-    <row r="123" ht="31.5" customHeight="1">
+    <row r="123" ht="21" customHeight="1">
       <c r="A123" s="8" t="inlineStr">
         <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>ÖP-15</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³, rotasyon kalıplı, temini, yerine konulması ve giriş-çıkış bağlantılarının yapılması</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+        </is>
+      </c>
+      <c r="B126" s="39" t="n"/>
+      <c r="C126" s="39" t="n"/>
+      <c r="D126" s="39" t="n"/>
+      <c r="E126" s="39" t="n"/>
+      <c r="F126" s="40" t="n"/>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Yapım İşinin Adı</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Birimi</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>Miktarı</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>48.02</v>
+      </c>
+    </row>
+    <row r="129" ht="31.5" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>1.922</v>
+      </c>
+    </row>
+    <row r="130" ht="31.5" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="B130" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E123" s="12" t="inlineStr">
+      <c r="E130" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F123" s="13" t="n">
-        <v>6.175</v>
-      </c>
-    </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+      <c r="F130" s="13" t="n">
+        <v>8.41</v>
+      </c>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="B131" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D131" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E124" s="12" t="inlineStr">
+      <c r="E131" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F124" s="13" t="n">
-        <v>41.4</v>
-      </c>
-    </row>
-    <row r="125" ht="21" customHeight="1">
-      <c r="A125" s="8" t="inlineStr">
+      <c r="F131" s="13" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="132" ht="21" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="B132" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D132" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="E132" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F125" s="13" t="n">
-        <v>0.587</v>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yem Silosu Betonarme Kaideleri &gt;   —   inşaat alanı 16.82 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
-        </is>
-      </c>
-      <c r="B128" s="39" t="n"/>
-      <c r="C128" s="39" t="n"/>
-      <c r="D128" s="39" t="n"/>
-      <c r="E128" s="39" t="n"/>
-      <c r="F128" s="40" t="n"/>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="F132" s="13" t="n">
+        <v>0.757</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
+        </is>
+      </c>
+      <c r="B135" s="39" t="n"/>
+      <c r="C135" s="39" t="n"/>
+      <c r="D135" s="39" t="n"/>
+      <c r="E135" s="39" t="n"/>
+      <c r="F135" s="40" t="n"/>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C136" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D136" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E136" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="B137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E130" s="12" t="inlineStr">
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F130" s="13" t="n">
-        <v>48.02</v>
-      </c>
-    </row>
-    <row r="131" ht="31.5" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+      <c r="F137" s="13" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="138" ht="31.5" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E131" s="12" t="inlineStr">
+      <c r="E138" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F131" s="13" t="n">
-        <v>1.922</v>
-      </c>
-    </row>
-    <row r="132" ht="31.5" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+      <c r="F138" s="13" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="139" ht="31.5" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B132" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="B139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D139" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E132" s="12" t="inlineStr">
+      <c r="E139" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F132" s="13" t="n">
-        <v>8.41</v>
-      </c>
-    </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="F139" s="13" t="n">
+        <v>15.15</v>
+      </c>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="B140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E133" s="12" t="inlineStr">
+      <c r="E140" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F133" s="13" t="n">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="134" ht="21" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+      <c r="F140" s="13" t="n">
+        <v>95.59999999999999</v>
+      </c>
+    </row>
+    <row r="141" ht="21" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E141" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F134" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="24" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
-        </is>
-      </c>
-      <c r="B137" s="39" t="n"/>
-      <c r="C137" s="39" t="n"/>
-      <c r="D137" s="39" t="n"/>
-      <c r="E137" s="39" t="n"/>
-      <c r="F137" s="40" t="n"/>
-    </row>
-    <row r="138" ht="28" customHeight="1">
-      <c r="A138" s="7" t="inlineStr">
+      <c r="F141" s="13" t="n">
+        <v>1.232</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="24" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
+        </is>
+      </c>
+      <c r="B144" s="39" t="n"/>
+      <c r="C144" s="39" t="n"/>
+      <c r="D144" s="39" t="n"/>
+      <c r="E144" s="39" t="n"/>
+      <c r="F144" s="40" t="n"/>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B145" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D145" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E138" s="7" t="inlineStr">
+      <c r="E145" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F138" s="7" t="inlineStr">
+      <c r="F145" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="14" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="B146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D146" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E139" s="12" t="inlineStr">
+      <c r="E146" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F139" s="13" t="n">
-        <v>106.5</v>
-      </c>
-    </row>
-    <row r="140" ht="31.5" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="F146" s="13" t="n">
+        <v>88.75</v>
+      </c>
+    </row>
+    <row r="147" ht="31.5" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F140" s="13" t="n">
-        <v>1.344</v>
-      </c>
-    </row>
-    <row r="141" ht="31.5" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="F147" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="148" ht="31.5" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D148" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E148" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F141" s="13" t="n">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="F148" s="13" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B142" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E142" s="12" t="inlineStr">
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F142" s="13" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="143" ht="21" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+      <c r="F149" s="13" t="n">
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="150" ht="21" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D150" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F143" s="13" t="n">
-        <v>1.232</v>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
-        </is>
-      </c>
-      <c r="B146" s="39" t="n"/>
-      <c r="C146" s="39" t="n"/>
-      <c r="D146" s="39" t="n"/>
-      <c r="E146" s="39" t="n"/>
-      <c r="F146" s="40" t="n"/>
-    </row>
-    <row r="147" ht="28" customHeight="1">
-      <c r="A147" s="7" t="inlineStr">
+      <c r="F150" s="13" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
+        </is>
+      </c>
+      <c r="B153" s="39" t="n"/>
+      <c r="C153" s="39" t="n"/>
+      <c r="D153" s="39" t="n"/>
+      <c r="E153" s="39" t="n"/>
+      <c r="F153" s="40" t="n"/>
+    </row>
+    <row r="154" ht="28" customHeight="1">
+      <c r="A154" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="B154" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C147" s="7" t="inlineStr">
+      <c r="C154" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D147" s="7" t="inlineStr">
+      <c r="D154" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E147" s="7" t="inlineStr">
+      <c r="E154" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F147" s="7" t="inlineStr">
+      <c r="F154" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="14" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
-        </is>
-      </c>
-      <c r="E148" s="12" t="inlineStr">
+      <c r="B155" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F148" s="13" t="n">
-        <v>88.75</v>
-      </c>
-    </row>
-    <row r="149" ht="31.5" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="F155" s="13" t="n">
+        <v>260.943</v>
+      </c>
+    </row>
+    <row r="156" ht="31.5" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D156" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F149" s="13" t="n">
-        <v>1.024</v>
-      </c>
-    </row>
-    <row r="150" ht="31.5" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E150" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="n">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" s="10" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
-        </is>
-      </c>
-      <c r="E151" s="12" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F151" s="13" t="n">
-        <v>79.8</v>
-      </c>
-    </row>
-    <row r="152" ht="21" customHeight="1">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E152" s="12" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F152" s="13" t="n">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="24" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
-        </is>
-      </c>
-      <c r="B155" s="39" t="n"/>
-      <c r="C155" s="39" t="n"/>
-      <c r="D155" s="39" t="n"/>
-      <c r="E155" s="39" t="n"/>
-      <c r="F155" s="40" t="n"/>
-    </row>
-    <row r="156" ht="28" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
-        </is>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C156" s="7" t="inlineStr">
-        <is>
-          <t>Poz No</t>
-        </is>
-      </c>
-      <c r="D156" s="7" t="inlineStr">
-        <is>
-          <t>Yapım İşinin Adı</t>
-        </is>
-      </c>
-      <c r="E156" s="7" t="inlineStr">
-        <is>
-          <t>Birimi</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>Miktarı</t>
-        </is>
+      <c r="F156" s="13" t="n">
+        <v>1.566</v>
       </c>
     </row>
     <row r="157" ht="14" customHeight="1">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B157" s="9" t="n">
@@ -4191,27 +4191,27 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F157" s="13" t="n">
-        <v>260.943</v>
-      </c>
-    </row>
-    <row r="158" ht="31.5" customHeight="1">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="158" ht="21" customHeight="1">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B158" s="9" t="n">
@@ -4219,27 +4219,27 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F158" s="13" t="n">
-        <v>1.566</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="159" ht="14" customHeight="1">
       <c r="A159" s="8" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
       <c r="B159" s="9" t="n">
@@ -4247,27 +4247,27 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>TKDK-0091</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F159" s="13" t="n">
-        <v>14.4</v>
+        <v>361.04</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
       <c r="A160" s="8" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B160" s="9" t="n">
@@ -4275,55 +4275,51 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F160" s="13" t="n">
-        <v>0.141</v>
+        <v>50</v>
       </c>
     </row>
     <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
-        <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
-        </is>
-      </c>
+      <c r="A161" s="15" t="n"/>
       <c r="B161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F161" s="13" t="n">
-        <v>361.04</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B162" s="9" t="n">
@@ -4331,36 +4327,36 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.100.1104</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F162" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="15" t="n"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" ht="21" customHeight="1">
+      <c r="A163" s="14" t="n"/>
       <c r="B163" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>15.560.1003</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -4369,26 +4365,22 @@
         </is>
       </c>
       <c r="F163" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
+      <c r="A164" s="14" t="n"/>
       <c r="B164" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>35.100.1104</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -4403,16 +4395,16 @@
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="14" t="n"/>
       <c r="B165" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>35.100.2106</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -4424,19 +4416,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" ht="21" customHeight="1">
+    <row r="166" ht="14" customHeight="1">
       <c r="A166" s="14" t="n"/>
       <c r="B166" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -4445,245 +4437,194 @@
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
       <c r="A167" s="14" t="n"/>
       <c r="B167" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F167" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" ht="14" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="168" ht="21" customHeight="1">
       <c r="A168" s="14" t="n"/>
       <c r="B168" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F168" s="13" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>35.140.3105</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F169" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="170" ht="21" customHeight="1">
-      <c r="A170" s="14" t="n"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="15" t="n"/>
       <c r="B170" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>35.140.3101</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F170" s="13" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="171" ht="21" customHeight="1">
-      <c r="A171" s="14" t="n"/>
-      <c r="B171" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C171" s="10" t="inlineStr">
-        <is>
-          <t>35.172.1706</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E171" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F171" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="15" t="n"/>
-      <c r="B172" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C172" s="10" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="D172" s="11" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E172" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F172" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="16" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B174" s="39" t="n"/>
-      <c r="C174" s="39" t="n"/>
-      <c r="D174" s="39" t="n"/>
-      <c r="E174" s="39" t="n"/>
-      <c r="F174" s="40" t="n"/>
+      <c r="B172" s="39" t="n"/>
+      <c r="C172" s="39" t="n"/>
+      <c r="D172" s="39" t="n"/>
+      <c r="E172" s="39" t="n"/>
+      <c r="F172" s="40" t="n"/>
+    </row>
+    <row r="173" ht="13" customHeight="1">
+      <c r="A173" s="17" t="inlineStr">
+        <is>
+          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="17" t="inlineStr">
+        <is>
+          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="13" customHeight="1">
       <c r="A175" s="17" t="inlineStr">
         <is>
-          <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="22" customHeight="1">
+          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="13" customHeight="1">
       <c r="A176" s="17" t="inlineStr">
         <is>
-          <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="13" customHeight="1">
-      <c r="A177" s="17" t="inlineStr">
-        <is>
-          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="13" customHeight="1">
-      <c r="A178" s="17" t="inlineStr">
-        <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="89">
     <mergeCell ref="A174:F174"/>
     <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A147"/>
     <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A156"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A155"/>
     <mergeCell ref="A175:F175"/>
     <mergeCell ref="A130"/>
     <mergeCell ref="A77"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A148"/>
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A157"/>
     <mergeCell ref="A123"/>
+    <mergeCell ref="A138"/>
     <mergeCell ref="A132"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A133"/>
     <mergeCell ref="A158"/>
     <mergeCell ref="A55"/>
     <mergeCell ref="A104"/>
-    <mergeCell ref="A160"/>
     <mergeCell ref="A150"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A162:A170"/>
     <mergeCell ref="A159"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A134"/>
-    <mergeCell ref="A152"/>
     <mergeCell ref="A121"/>
-    <mergeCell ref="A164:A172"/>
-    <mergeCell ref="A161"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A31"/>
     <mergeCell ref="A58"/>
     <mergeCell ref="A79:A97"/>
     <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A124"/>
-    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A146"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="A149"/>
-    <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A151"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="A141"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A122"/>
-    <mergeCell ref="A125"/>
-    <mergeCell ref="A136:F136"/>
-    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A112"/>
-    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="A30"/>
     <mergeCell ref="A114"/>
@@ -4691,14 +4632,17 @@
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A137"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="A56"/>
     <mergeCell ref="A139"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A129"/>
     <mergeCell ref="A116"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A131"/>
-    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A140"/>
     <mergeCell ref="A10"/>
     <mergeCell ref="A115"/>
@@ -4706,19 +4650,17 @@
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="A67:A69"/>
     <mergeCell ref="A9"/>
-    <mergeCell ref="A143"/>
-    <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
     <mergeCell ref="A103"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A78"/>
-    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="A160:A161"/>
+    <mergeCell ref="A128"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A32:A50"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A105"/>
     <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A146:F146"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A57"/>
     <mergeCell ref="A6:F6"/>

--- a/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
+++ b/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
@@ -186,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +280,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -694,11 +697,11 @@
           <t>14,00 x 79,00 = 1.106,00 m²; betonarme şerit temel, çelik karkas üstyapı, sandviç panel çatı.</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n"/>
-      <c r="C6" s="39" t="n"/>
-      <c r="D6" s="39" t="n"/>
-      <c r="E6" s="39" t="n"/>
-      <c r="F6" s="40" t="n"/>
+      <c r="B6" s="40" t="n"/>
+      <c r="C6" s="40" t="n"/>
+      <c r="D6" s="40" t="n"/>
+      <c r="E6" s="40" t="n"/>
+      <c r="F6" s="41" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1833,11 +1836,11 @@
           <t>A blok ile geometrik olarak birebir aynıdır.</t>
         </is>
       </c>
-      <c r="B53" s="39" t="n"/>
-      <c r="C53" s="39" t="n"/>
-      <c r="D53" s="39" t="n"/>
-      <c r="E53" s="39" t="n"/>
-      <c r="F53" s="40" t="n"/>
+      <c r="B53" s="40" t="n"/>
+      <c r="C53" s="40" t="n"/>
+      <c r="D53" s="40" t="n"/>
+      <c r="E53" s="40" t="n"/>
+      <c r="F53" s="41" t="n"/>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -2972,11 +2975,11 @@
           <t>Dış ölçü 11,50 x 10,00 m; betonarme radye, perde ve üst döşeme.</t>
         </is>
       </c>
-      <c r="B100" s="39" t="n"/>
-      <c r="C100" s="39" t="n"/>
-      <c r="D100" s="39" t="n"/>
-      <c r="E100" s="39" t="n"/>
-      <c r="F100" s="40" t="n"/>
+      <c r="B100" s="40" t="n"/>
+      <c r="C100" s="40" t="n"/>
+      <c r="D100" s="40" t="n"/>
+      <c r="E100" s="40" t="n"/>
+      <c r="F100" s="41" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -3187,11 +3190,11 @@
           <t>Dış ölçü 6,00 x 3,00 m, betonarme sızdırmaz çukur.</t>
         </is>
       </c>
-      <c r="B110" s="39" t="n"/>
-      <c r="C110" s="39" t="n"/>
-      <c r="D110" s="39" t="n"/>
-      <c r="E110" s="39" t="n"/>
-      <c r="F110" s="40" t="n"/>
+      <c r="B110" s="40" t="n"/>
+      <c r="C110" s="40" t="n"/>
+      <c r="D110" s="40" t="n"/>
+      <c r="E110" s="40" t="n"/>
+      <c r="F110" s="41" t="n"/>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -3378,11 +3381,11 @@
           <t>Prefabrik polietilen sızdırmaz foseptik tankı, 6 m³; kazı ve grobeton oturma yatağı üzerine yerleştirilir (çukur dış ölçüsü 2,00 x 2,00 m).</t>
         </is>
       </c>
-      <c r="B119" s="39" t="n"/>
-      <c r="C119" s="39" t="n"/>
-      <c r="D119" s="39" t="n"/>
-      <c r="E119" s="39" t="n"/>
-      <c r="F119" s="40" t="n"/>
+      <c r="B119" s="40" t="n"/>
+      <c r="C119" s="40" t="n"/>
+      <c r="D119" s="40" t="n"/>
+      <c r="E119" s="40" t="n"/>
+      <c r="F119" s="41" t="n"/>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
@@ -3513,11 +3516,11 @@
           <t>2 adet, her biri 2,90 x 2,90 m.</t>
         </is>
       </c>
-      <c r="B126" s="39" t="n"/>
-      <c r="C126" s="39" t="n"/>
-      <c r="D126" s="39" t="n"/>
-      <c r="E126" s="39" t="n"/>
-      <c r="F126" s="40" t="n"/>
+      <c r="B126" s="40" t="n"/>
+      <c r="C126" s="40" t="n"/>
+      <c r="D126" s="40" t="n"/>
+      <c r="E126" s="40" t="n"/>
+      <c r="F126" s="41" t="n"/>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -3704,11 +3707,11 @@
           <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
         </is>
       </c>
-      <c r="B135" s="39" t="n"/>
-      <c r="C135" s="39" t="n"/>
-      <c r="D135" s="39" t="n"/>
-      <c r="E135" s="39" t="n"/>
-      <c r="F135" s="40" t="n"/>
+      <c r="B135" s="40" t="n"/>
+      <c r="C135" s="40" t="n"/>
+      <c r="D135" s="40" t="n"/>
+      <c r="E135" s="40" t="n"/>
+      <c r="F135" s="41" t="n"/>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
@@ -3895,11 +3898,11 @@
           <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
         </is>
       </c>
-      <c r="B144" s="39" t="n"/>
-      <c r="C144" s="39" t="n"/>
-      <c r="D144" s="39" t="n"/>
-      <c r="E144" s="39" t="n"/>
-      <c r="F144" s="40" t="n"/>
+      <c r="B144" s="40" t="n"/>
+      <c r="C144" s="40" t="n"/>
+      <c r="D144" s="40" t="n"/>
+      <c r="E144" s="40" t="n"/>
+      <c r="F144" s="41" t="n"/>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -4086,11 +4089,11 @@
           <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
         </is>
       </c>
-      <c r="B153" s="39" t="n"/>
-      <c r="C153" s="39" t="n"/>
-      <c r="D153" s="39" t="n"/>
-      <c r="E153" s="39" t="n"/>
-      <c r="F153" s="40" t="n"/>
+      <c r="B153" s="40" t="n"/>
+      <c r="C153" s="40" t="n"/>
+      <c r="D153" s="40" t="n"/>
+      <c r="E153" s="40" t="n"/>
+      <c r="F153" s="41" t="n"/>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="7" t="inlineStr">
@@ -4542,11 +4545,11 @@
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B172" s="39" t="n"/>
-      <c r="C172" s="39" t="n"/>
-      <c r="D172" s="39" t="n"/>
-      <c r="E172" s="39" t="n"/>
-      <c r="F172" s="40" t="n"/>
+      <c r="B172" s="40" t="n"/>
+      <c r="C172" s="40" t="n"/>
+      <c r="D172" s="40" t="n"/>
+      <c r="E172" s="40" t="n"/>
+      <c r="F172" s="41" t="n"/>
     </row>
     <row r="173" ht="13" customHeight="1">
       <c r="A173" s="17" t="inlineStr">

--- a/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
+++ b/belgeler/27_KESIF_OZETI_TUM_YAPILAR.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3513,7 +3513,7 @@
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>2 adet, her biri 2,90 x 2,90 m.</t>
+          <t>2 adet; her biri 2,90 x 2,90 m radye temel (H = 0,40 m, kot -0,10 / +0,30) ve üzerinde 4 adet SB01…SB04 kolonu (40/40, kot +0,30 / +1,40).</t>
         </is>
       </c>
       <c r="B126" s="40" t="n"/>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>48.02</v>
+        <v>6.084</v>
       </c>
     </row>
     <row r="129" ht="31.5" customHeight="1">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>8.41</v>
+        <v>8.135999999999999</v>
       </c>
     </row>
     <row r="131" ht="14" customHeight="1">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>11.6</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -3691,675 +3691,675 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.757</v>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+        <v>0.543</v>
+      </c>
+    </row>
+    <row r="133" ht="21" customHeight="1">
+      <c r="A133" s="15" t="n"/>
+      <c r="B133" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>&lt; Su Deposu &gt;   —   inşaat alanı 12.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 4,00 x 3,00 m, betonarme.</t>
         </is>
       </c>
-      <c r="B135" s="40" t="n"/>
-      <c r="C135" s="40" t="n"/>
-      <c r="D135" s="40" t="n"/>
-      <c r="E135" s="40" t="n"/>
-      <c r="F135" s="41" t="n"/>
-    </row>
-    <row r="136" ht="28" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
+      <c r="B136" s="40" t="n"/>
+      <c r="C136" s="40" t="n"/>
+      <c r="D136" s="40" t="n"/>
+      <c r="E136" s="40" t="n"/>
+      <c r="F136" s="41" t="n"/>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
+      <c r="F137" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="B138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D138" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E137" s="12" t="inlineStr">
+      <c r="E138" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F137" s="13" t="n">
+      <c r="F138" s="13" t="n">
         <v>106.5</v>
-      </c>
-    </row>
-    <row r="138" ht="31.5" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B138" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E138" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F138" s="13" t="n">
-        <v>1.344</v>
       </c>
     </row>
     <row r="139" ht="31.5" customHeight="1">
       <c r="A139" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>1.344</v>
+      </c>
+    </row>
+    <row r="140" ht="31.5" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
+      <c r="B140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D140" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E139" s="12" t="inlineStr">
+      <c r="E140" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F139" s="13" t="n">
+      <c r="F140" s="13" t="n">
         <v>15.15</v>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B140" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="B141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D141" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E140" s="12" t="inlineStr">
+      <c r="E141" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F140" s="13" t="n">
+      <c r="F141" s="13" t="n">
         <v>95.59999999999999</v>
       </c>
     </row>
-    <row r="141" ht="21" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="142" ht="21" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
+      <c r="B142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D142" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E142" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F141" s="13" t="n">
+      <c r="F142" s="13" t="n">
         <v>1.232</v>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>&lt; Yağmur Suyu Deposu &gt;   —   inşaat alanı 9.00 m²</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="24" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>Dış ölçü 3,00 x 3,00 m, betonarme; sıhhi tesisat projesindeki yağmur suyu geri kazanım deposunun haznesi.</t>
         </is>
       </c>
-      <c r="B144" s="40" t="n"/>
-      <c r="C144" s="40" t="n"/>
-      <c r="D144" s="40" t="n"/>
-      <c r="E144" s="40" t="n"/>
-      <c r="F144" s="41" t="n"/>
-    </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+      <c r="B145" s="40" t="n"/>
+      <c r="C145" s="40" t="n"/>
+      <c r="D145" s="40" t="n"/>
+      <c r="E145" s="40" t="n"/>
+      <c r="F145" s="41" t="n"/>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="B146" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C146" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="E146" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
+      <c r="F146" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B146" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="B147" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>15.120.1101</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D147" s="11" t="inlineStr">
         <is>
           <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E147" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F146" s="13" t="n">
+      <c r="F147" s="13" t="n">
         <v>88.75</v>
-      </c>
-    </row>
-    <row r="147" ht="31.5" customHeight="1">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F147" s="13" t="n">
-        <v>1.024</v>
       </c>
     </row>
     <row r="148" ht="31.5" customHeight="1">
       <c r="A148" s="8" t="inlineStr">
         <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="n">
+        <v>1.024</v>
+      </c>
+    </row>
+    <row r="149" ht="31.5" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B148" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C148" s="10" t="inlineStr">
+      <c r="B149" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
+      <c r="D149" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E148" s="12" t="inlineStr">
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F148" s="13" t="n">
+      <c r="F149" s="13" t="n">
         <v>12.3</v>
       </c>
     </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
+      <c r="B150" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D149" s="11" t="inlineStr">
+      <c r="D150" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="E150" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F149" s="13" t="n">
+      <c r="F150" s="13" t="n">
         <v>79.8</v>
       </c>
     </row>
-    <row r="150" ht="21" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
+    <row r="151" ht="21" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
+      <c r="B151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D150" s="11" t="inlineStr">
+      <c r="D151" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E150" s="12" t="inlineStr">
+      <c r="E151" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F150" s="13" t="n">
+      <c r="F151" s="13" t="n">
         <v>1.23</v>
       </c>
     </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="4" t="inlineStr">
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>&lt; Çevre Düzenlemesi ve Saha Altyapısı &gt;</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+    <row r="154" ht="24" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>Parsel çevresi çit, tesis içi yol platformu ve yapılar arası altyapı hatları.</t>
         </is>
       </c>
-      <c r="B153" s="40" t="n"/>
-      <c r="C153" s="40" t="n"/>
-      <c r="D153" s="40" t="n"/>
-      <c r="E153" s="40" t="n"/>
-      <c r="F153" s="41" t="n"/>
-    </row>
-    <row r="154" ht="28" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
+      <c r="B154" s="40" t="n"/>
+      <c r="C154" s="40" t="n"/>
+      <c r="D154" s="40" t="n"/>
+      <c r="E154" s="40" t="n"/>
+      <c r="F154" s="41" t="n"/>
+    </row>
+    <row r="155" ht="28" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>Uygun Harcama Kaleminin EK-1'de yer alan adı</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C154" s="7" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
         <is>
           <t>Poz No</t>
         </is>
       </c>
-      <c r="D154" s="7" t="inlineStr">
+      <c r="D155" s="7" t="inlineStr">
         <is>
           <t>Yapım İşinin Adı</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t>Birimi</t>
         </is>
       </c>
-      <c r="F154" s="7" t="inlineStr">
+      <c r="F155" s="7" t="inlineStr">
         <is>
           <t>Miktarı</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="8" t="inlineStr">
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
+      <c r="B156" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
         <is>
           <t>15.120.1001</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr">
+      <c r="D156" s="11" t="inlineStr">
         <is>
           <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
-      <c r="E155" s="12" t="inlineStr">
+      <c r="E156" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F155" s="13" t="n">
+      <c r="F156" s="13" t="n">
         <v>260.943</v>
       </c>
     </row>
-    <row r="156" ht="31.5" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="157" ht="31.5" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B156" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="B157" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D157" s="11" t="inlineStr">
         <is>
           <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
-      <c r="E156" s="12" t="inlineStr">
+      <c r="E157" s="12" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F156" s="13" t="n">
+      <c r="F157" s="13" t="n">
         <v>1.566</v>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
         <is>
           <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
-      <c r="B157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
+      <c r="B158" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" s="10" t="inlineStr">
         <is>
           <t>15.180.1003</t>
         </is>
       </c>
-      <c r="D157" s="11" t="inlineStr">
+      <c r="D158" s="11" t="inlineStr">
         <is>
           <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
-      <c r="E157" s="12" t="inlineStr">
+      <c r="E158" s="12" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="F157" s="13" t="n">
+      <c r="F158" s="13" t="n">
         <v>14.4</v>
       </c>
     </row>
-    <row r="158" ht="21" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
+    <row r="159" ht="21" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
         </is>
       </c>
-      <c r="B158" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="B159" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
         <is>
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="D158" s="11" t="inlineStr">
+      <c r="D159" s="11" t="inlineStr">
         <is>
           <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
-      <c r="E158" s="12" t="inlineStr">
+      <c r="E159" s="12" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F158" s="13" t="n">
+      <c r="F159" s="13" t="n">
         <v>0.141</v>
       </c>
     </row>
-    <row r="159" ht="14" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
-      <c r="B159" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
+      <c r="B160" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
         <is>
           <t>TKDK-0091</t>
         </is>
       </c>
-      <c r="D159" s="11" t="inlineStr">
+      <c r="D160" s="11" t="inlineStr">
         <is>
           <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
-      <c r="E159" s="12" t="inlineStr">
+      <c r="E160" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F159" s="13" t="n">
+      <c r="F160" s="13" t="n">
         <v>361.04</v>
       </c>
     </row>
-    <row r="160" ht="21" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
+    <row r="161" ht="21" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t>Kanalizasyon işleri</t>
         </is>
       </c>
-      <c r="B160" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" s="10" t="inlineStr">
+      <c r="B161" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>43.527.1001</t>
         </is>
       </c>
-      <c r="D160" s="11" t="inlineStr">
+      <c r="D161" s="11" t="inlineStr">
         <is>
           <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
-      <c r="E160" s="12" t="inlineStr">
+      <c r="E161" s="12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F160" s="13" t="n">
+      <c r="F161" s="13" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="15" t="n"/>
-      <c r="B161" s="9" t="n">
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="15" t="n"/>
+      <c r="B162" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C161" s="10" t="inlineStr">
+      <c r="C162" s="10" t="inlineStr">
         <is>
           <t>15.560.1003</t>
         </is>
       </c>
-      <c r="D161" s="11" t="inlineStr">
+      <c r="D162" s="11" t="inlineStr">
         <is>
           <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
-      <c r="E161" s="12" t="inlineStr">
+      <c r="E162" s="12" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F161" s="13" t="n">
+      <c r="F162" s="13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="162" ht="21" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+    <row r="163" ht="21" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B162" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
+      <c r="B163" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>35.100.1104</t>
         </is>
       </c>
-      <c r="D162" s="11" t="inlineStr">
+      <c r="D163" s="11" t="inlineStr">
         <is>
           <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E162" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F162" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" ht="21" customHeight="1">
-      <c r="A163" s="14" t="n"/>
-      <c r="B163" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
-        <is>
-          <t>35.100.2106</t>
-        </is>
-      </c>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E163" s="12" t="inlineStr">
@@ -4374,16 +4374,16 @@
     <row r="164" ht="21" customHeight="1">
       <c r="A164" s="14" t="n"/>
       <c r="B164" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E164" s="12" t="inlineStr">
@@ -4398,16 +4398,16 @@
     <row r="165" ht="21" customHeight="1">
       <c r="A165" s="14" t="n"/>
       <c r="B165" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E165" s="12" t="inlineStr">
@@ -4419,19 +4419,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" ht="14" customHeight="1">
+    <row r="166" ht="21" customHeight="1">
       <c r="A166" s="14" t="n"/>
       <c r="B166" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E166" s="12" t="inlineStr">
@@ -4440,46 +4440,46 @@
         </is>
       </c>
       <c r="F166" s="13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" ht="21" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" ht="14" customHeight="1">
       <c r="A167" s="14" t="n"/>
       <c r="B167" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>35.140.3105</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F167" s="13" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1">
       <c r="A168" s="14" t="n"/>
       <c r="B168" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>35.140.3101</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E168" s="12" t="inlineStr">
@@ -4494,40 +4494,40 @@
     <row r="169" ht="21" customHeight="1">
       <c r="A169" s="14" t="n"/>
       <c r="B169" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>35.140.3101</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E169" s="12" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F169" s="13" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="170" ht="21" customHeight="1">
+      <c r="A170" s="14" t="n"/>
+      <c r="B170" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C169" s="10" t="inlineStr">
+      <c r="C170" s="10" t="inlineStr">
         <is>
           <t>35.172.1706</t>
         </is>
       </c>
-      <c r="D169" s="11" t="inlineStr">
+      <c r="D170" s="11" t="inlineStr">
         <is>
           <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E169" s="12" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F169" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="15" t="n"/>
-      <c r="B170" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="C170" s="10" t="inlineStr">
-        <is>
-          <t>35.170.4002</t>
-        </is>
-      </c>
-      <c r="D170" s="11" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
@@ -4539,41 +4539,65 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="16" t="inlineStr">
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="15" t="n"/>
+      <c r="B171" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>35.170.4002</t>
+        </is>
+      </c>
+      <c r="D171" s="11" t="inlineStr">
+        <is>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E171" s="12" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B172" s="40" t="n"/>
-      <c r="C172" s="40" t="n"/>
-      <c r="D172" s="40" t="n"/>
-      <c r="E172" s="40" t="n"/>
-      <c r="F172" s="41" t="n"/>
-    </row>
-    <row r="173" ht="13" customHeight="1">
-      <c r="A173" s="17" t="inlineStr">
+      <c r="B173" s="40" t="n"/>
+      <c r="C173" s="40" t="n"/>
+      <c r="D173" s="40" t="n"/>
+      <c r="E173" s="40" t="n"/>
+      <c r="F173" s="41" t="n"/>
+    </row>
+    <row r="174" ht="13" customHeight="1">
+      <c r="A174" s="17" t="inlineStr">
         <is>
           <t>•  Keşif özetinde birim fiyat ve tutar sütunu bulunmaz; bunlar teklif davet mektubu ekindeki ayrı cetvelde yer alır.</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="17" t="inlineStr">
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="17" t="inlineStr">
         <is>
           <t>•  YEŞİL zemindeki poz numaraları TKDK'nın 17.02.2026 tarihli Özel Poz Tablosundan, renksiz olanlar Çevre, Şehircilik ve İklim Değişikliği Bakanlığı 2026 birim fiyat kitabından alınmıştır. Keşifteki her kalem bir birim fiyat kitabı pozudur.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="13" customHeight="1">
-      <c r="A175" s="17" t="inlineStr">
-        <is>
-          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
         </is>
       </c>
     </row>
     <row r="176" ht="13" customHeight="1">
       <c r="A176" s="17" t="inlineStr">
+        <is>
+          <t>•  Kümes A ve B blok özdeş olduğundan tek başlık altında toplanmıştır; miktarlar iki bloğun toplamıdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="13" customHeight="1">
+      <c r="A177" s="17" t="inlineStr">
         <is>
           <t>•  Elektrik tesisatı bölümü, kuvvetli akım birim fiyat listesi temin edildikten sonra tamamlanacaktır.</t>
         </is>
@@ -4588,7 +4612,7 @@
     <mergeCell ref="A156"/>
     <mergeCell ref="A23:A25"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A155"/>
+    <mergeCell ref="A163:A171"/>
     <mergeCell ref="A175:F175"/>
     <mergeCell ref="A130"/>
     <mergeCell ref="A77"/>
@@ -4598,16 +4622,12 @@
     <mergeCell ref="A157"/>
     <mergeCell ref="A123"/>
     <mergeCell ref="A138"/>
-    <mergeCell ref="A132"/>
-    <mergeCell ref="A134:F134"/>
-    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A70:A72"/>
     <mergeCell ref="A158"/>
     <mergeCell ref="A55"/>
     <mergeCell ref="A104"/>
+    <mergeCell ref="A160"/>
     <mergeCell ref="A150"/>
-    <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A162:A170"/>
     <mergeCell ref="A159"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A99:F99"/>
@@ -4620,14 +4640,18 @@
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A146"/>
     <mergeCell ref="A176:F176"/>
     <mergeCell ref="A149"/>
     <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A151"/>
     <mergeCell ref="A141"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A122"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A145:F145"/>
     <mergeCell ref="A112"/>
+    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="A30"/>
     <mergeCell ref="A114"/>
@@ -4636,14 +4660,14 @@
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A173:F173"/>
-    <mergeCell ref="A137"/>
-    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="A56"/>
     <mergeCell ref="A139"/>
+    <mergeCell ref="A161:A162"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A129"/>
     <mergeCell ref="A116"/>
+    <mergeCell ref="A132:A133"/>
     <mergeCell ref="A8"/>
     <mergeCell ref="A131"/>
     <mergeCell ref="A140"/>
@@ -4653,11 +4677,11 @@
     <mergeCell ref="A75:A76"/>
     <mergeCell ref="A67:A69"/>
     <mergeCell ref="A9"/>
+    <mergeCell ref="A142"/>
     <mergeCell ref="A11"/>
     <mergeCell ref="A103"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A78"/>
-    <mergeCell ref="A160:A161"/>
     <mergeCell ref="A128"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="A32:A50"/>
